--- a/Semiconductor/MRVL.xlsx
+++ b/Semiconductor/MRVL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameel/Library/CloudStorage/Dropbox/models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFE303E-F7EE-704B-B3D0-71CC7FE91EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1D233B-D0D3-0B4F-940A-45729E07A596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1800" yWindow="680" windowWidth="27640" windowHeight="22520" xr2:uid="{18A14933-2D54-E947-909F-6FBE03556AEE}"/>
+    <workbookView xWindow="22300" yWindow="860" windowWidth="45180" windowHeight="26580" activeTab="1" xr2:uid="{18A14933-2D54-E947-909F-6FBE03556AEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="128">
   <si>
     <t>P</t>
   </si>
@@ -297,9 +297,6 @@
     <t xml:space="preserve">FCF </t>
   </si>
   <si>
-    <t>4Q</t>
-  </si>
-  <si>
     <t>% R&amp;D</t>
   </si>
   <si>
@@ -364,15 +361,118 @@
   </si>
   <si>
     <t xml:space="preserve">Upside </t>
+  </si>
+  <si>
+    <t>GM%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4Q Moving NI </t>
+  </si>
+  <si>
+    <t>4Q Moving FCF</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash </t>
+  </si>
+  <si>
+    <t>A/R</t>
+  </si>
+  <si>
+    <t>Inventories</t>
+  </si>
+  <si>
+    <t>Prepaid Exp</t>
+  </si>
+  <si>
+    <t>PPE</t>
+  </si>
+  <si>
+    <t>Goodwill</t>
+  </si>
+  <si>
+    <t>Acquired intangibles</t>
+  </si>
+  <si>
+    <t>Deferred Tx Assets</t>
+  </si>
+  <si>
+    <t>ONCA</t>
+  </si>
+  <si>
+    <t>TL</t>
+  </si>
+  <si>
+    <t>A/P</t>
+  </si>
+  <si>
+    <t>Accrued Liab</t>
+  </si>
+  <si>
+    <t>Accrued employee comp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short term debt </t>
+  </si>
+  <si>
+    <t>LTD</t>
+  </si>
+  <si>
+    <t>ONCL</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>TL + E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Debt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Cash </t>
+  </si>
+  <si>
+    <t>Book Value</t>
+  </si>
+  <si>
+    <t>Current Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets Held 4 sale </t>
+  </si>
+  <si>
+    <t>Growth YY</t>
+  </si>
+  <si>
+    <t>Quick Ratio</t>
+  </si>
+  <si>
+    <t>Inventory / Rev</t>
+  </si>
+  <si>
+    <t>DIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSO </t>
+  </si>
+  <si>
+    <t>DPO</t>
+  </si>
+  <si>
+    <t>CCC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="m/d;@"/>
+    <numFmt numFmtId="169" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -451,7 +551,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -459,11 +559,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -488,6 +617,14 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,9 +653,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>21772</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>87086</xdr:rowOff>
+      <xdr:colOff>108857</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>36286</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -533,8 +670,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13019314" y="508000"/>
-          <a:ext cx="29029" cy="6589486"/>
+          <a:off x="11903528" y="497114"/>
+          <a:ext cx="116115" cy="15867743"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -559,16 +696,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>7257</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>497114</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>21771</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>14514</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>87086</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>136072</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>117928</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -583,8 +720,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5500914" y="21771"/>
-          <a:ext cx="7257" cy="7075715"/>
+          <a:off x="6420757" y="0"/>
+          <a:ext cx="146958" cy="17426214"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -955,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>122.82</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="2:10">
@@ -963,10 +1100,10 @@
         <v>1</v>
       </c>
       <c r="I5" s="1">
-        <v>862.2</v>
+        <v>848.1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="2:10">
@@ -975,7 +1112,7 @@
       </c>
       <c r="I6" s="1">
         <f>+I5*I4</f>
-        <v>105895.40399999999</v>
+        <v>69544.2</v>
       </c>
     </row>
     <row r="7" spans="2:10">
@@ -983,11 +1120,11 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>885.9</v>
+        <v>2714.5</v>
       </c>
       <c r="J7" s="1" t="str">
         <f>+J5</f>
-        <v>Q125</v>
+        <v>Q326</v>
       </c>
     </row>
     <row r="8" spans="2:10">
@@ -998,12 +1135,12 @@
         <v>4</v>
       </c>
       <c r="I8" s="1">
-        <f>1255.2+2977.4</f>
-        <v>4232.6000000000004</v>
+        <f>499.5+3969.4</f>
+        <v>4468.8999999999996</v>
       </c>
       <c r="J8" s="1" t="str">
         <f>+J7</f>
-        <v>Q125</v>
+        <v>Q326</v>
       </c>
     </row>
     <row r="9" spans="2:10">
@@ -1018,7 +1155,7 @@
       </c>
       <c r="I9" s="1">
         <f>+I6-I7+I8</f>
-        <v>109242.10400000001</v>
+        <v>71298.599999999991</v>
       </c>
     </row>
     <row r="10" spans="2:10">
@@ -1187,19 +1324,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6512B788-DF08-3043-8B9E-179193172FFF}">
-  <dimension ref="B2:IA48"/>
+  <dimension ref="A2:IA86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="1" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="10.83203125" style="1"/>
     <col min="17" max="18" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="25" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="34" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="34" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="41" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -1229,7 +1367,10 @@
         <v>45598</v>
       </c>
       <c r="L2" s="7">
-        <v>45775</v>
+        <v>45871</v>
+      </c>
+      <c r="M2" s="7">
+        <v>47058</v>
       </c>
     </row>
     <row r="3" spans="2:235" s="3" customFormat="1">
@@ -1258,16 +1399,16 @@
         <v>39</v>
       </c>
       <c r="K3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="Q3" s="3">
         <v>2018</v>
@@ -2143,7 +2284,7 @@
     </row>
     <row r="4" spans="2:235" s="3" customFormat="1">
       <c r="B4" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G4" s="3">
         <v>529.9</v>
@@ -2154,7 +2295,7 @@
     </row>
     <row r="5" spans="2:235" s="3" customFormat="1">
       <c r="B5" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G5" s="3">
         <v>42.6</v>
@@ -2165,7 +2306,7 @@
     </row>
     <row r="6" spans="2:235" s="3" customFormat="1">
       <c r="B6" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" s="3">
         <v>216.5</v>
@@ -2176,7 +2317,7 @@
     </row>
     <row r="7" spans="2:235" s="3" customFormat="1">
       <c r="B7" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3">
         <v>111.3</v>
@@ -2187,7 +2328,7 @@
     </row>
     <row r="8" spans="2:235" s="3" customFormat="1">
       <c r="B8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3">
         <v>6.8</v>
@@ -2198,7 +2339,7 @@
     </row>
     <row r="9" spans="2:235" s="3" customFormat="1">
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G9" s="3">
         <v>17.3</v>
@@ -2209,7 +2350,7 @@
     </row>
     <row r="10" spans="2:235" s="3" customFormat="1">
       <c r="B10" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3">
         <v>65</v>
@@ -2220,7 +2361,7 @@
     </row>
     <row r="11" spans="2:235" s="3" customFormat="1">
       <c r="B11" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3">
         <v>22.4</v>
@@ -2231,7 +2372,7 @@
     </row>
     <row r="12" spans="2:235" s="3" customFormat="1">
       <c r="B12" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G12" s="3">
         <v>53</v>
@@ -2242,7 +2383,7 @@
     </row>
     <row r="13" spans="2:235" s="3" customFormat="1">
       <c r="B13" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G13" s="3">
         <v>96.4</v>
@@ -2284,6 +2425,12 @@
       <c r="K15" s="1">
         <v>1440.6</v>
       </c>
+      <c r="L15" s="1">
+        <v>1490.5</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1517.9</v>
+      </c>
       <c r="S15" s="1">
         <v>823.84100000000001</v>
       </c>
@@ -2335,6 +2482,12 @@
       <c r="K16" s="1">
         <v>177.5</v>
       </c>
+      <c r="L16" s="1">
+        <v>193.6</v>
+      </c>
+      <c r="M16" s="1">
+        <v>237.2</v>
+      </c>
       <c r="S16" s="1">
         <v>369.90100000000001</v>
       </c>
@@ -2354,7 +2507,7 @@
         <v>626.4</v>
       </c>
     </row>
-    <row r="17" spans="2:235">
+    <row r="17" spans="1:235">
       <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
@@ -2386,6 +2539,12 @@
       <c r="K17" s="1">
         <v>138.4</v>
       </c>
+      <c r="L17" s="1">
+        <v>130.1</v>
+      </c>
+      <c r="M17" s="1">
+        <v>167.8</v>
+      </c>
       <c r="S17" s="1">
         <v>569.57399999999996</v>
       </c>
@@ -2405,7 +2564,7 @@
         <v>338.2</v>
       </c>
     </row>
-    <row r="18" spans="2:235">
+    <row r="18" spans="1:235">
       <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
@@ -2437,6 +2596,12 @@
       <c r="K18" s="1">
         <v>63.1</v>
       </c>
+      <c r="L18" s="1">
+        <v>115.9</v>
+      </c>
+      <c r="M18" s="1">
+        <v>116.6</v>
+      </c>
       <c r="S18" s="1">
         <v>845.82500000000005</v>
       </c>
@@ -2456,7 +2621,7 @@
         <v>316.10000000000002</v>
       </c>
     </row>
-    <row r="19" spans="2:235" s="6" customFormat="1">
+    <row r="19" spans="1:235" s="6" customFormat="1">
       <c r="B19" s="6" t="s">
         <v>24</v>
       </c>
@@ -2488,6 +2653,12 @@
       <c r="K19" s="6">
         <v>75.7</v>
       </c>
+      <c r="L19" s="6">
+        <v>76</v>
+      </c>
+      <c r="M19" s="6">
+        <v>35</v>
+      </c>
       <c r="S19" s="6">
         <v>90.02</v>
       </c>
@@ -2507,119 +2678,123 @@
         <v>322.39999999999998</v>
       </c>
     </row>
-    <row r="20" spans="2:235">
-      <c r="B20" s="5" t="s">
+    <row r="20" spans="1:235">
+      <c r="A20" s="19"/>
+      <c r="B20" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="19">
         <v>1321.7</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="19">
         <v>1340.9</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="19">
         <v>1418.6</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="19">
         <f>+W20-SUM(C20:E20)</f>
         <v>1426.4999999999995</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="19">
         <f>SUM(G15:G19)</f>
         <v>1160.8999999999999</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="19">
         <v>1272.9000000000001</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="19">
         <v>1516.1</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="19">
         <f t="shared" si="201"/>
         <v>1817.3999999999992</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="19">
         <f>SUM(K15:K19)</f>
         <v>1895.3</v>
       </c>
-      <c r="L20" s="1">
-        <f>+K20</f>
-        <v>1895.3</v>
-      </c>
-      <c r="M20" s="1">
-        <f>+L20</f>
-        <v>1895.3</v>
-      </c>
-      <c r="N20" s="1">
-        <f>+M20</f>
-        <v>1895.3</v>
-      </c>
-      <c r="S20" s="1">
+      <c r="L20" s="19">
+        <f>SUM(L15:L19)</f>
+        <v>2006.1</v>
+      </c>
+      <c r="M20" s="19">
+        <f>SUM(M15:M19)</f>
+        <v>2074.5</v>
+      </c>
+      <c r="N20" s="19">
+        <v>2200</v>
+      </c>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19">
         <f t="shared" ref="S20:X20" si="202">+SUM(S15:S19)</f>
         <v>2699.1609999999996</v>
       </c>
-      <c r="T20" s="1">
+      <c r="T20" s="19">
         <f t="shared" si="202"/>
         <v>2968.8999999999996</v>
       </c>
-      <c r="U20" s="1">
+      <c r="U20" s="19">
         <f t="shared" si="202"/>
         <v>4462.4000000000005</v>
       </c>
-      <c r="V20" s="1">
+      <c r="V20" s="19">
         <f t="shared" si="202"/>
         <v>5919.6</v>
       </c>
-      <c r="W20" s="1">
+      <c r="W20" s="19">
         <f t="shared" si="202"/>
         <v>5507.7</v>
       </c>
-      <c r="X20" s="1">
+      <c r="X20" s="19">
         <f t="shared" si="202"/>
         <v>5767.2999999999993</v>
       </c>
-      <c r="Y20" s="1">
-        <f>+K20*4</f>
-        <v>7581.2</v>
-      </c>
-      <c r="Z20" s="1">
-        <f>+Y20*1.2</f>
-        <v>9097.4399999999987</v>
-      </c>
-      <c r="AA20" s="1">
-        <f t="shared" ref="AA20:AH20" si="203">+Z20*1.2</f>
-        <v>10916.927999999998</v>
-      </c>
-      <c r="AB20" s="1">
+      <c r="Y20" s="19">
+        <f>SUM(K20:N20)</f>
+        <v>8175.9</v>
+      </c>
+      <c r="Z20" s="19">
+        <f>+Y20*1.03</f>
+        <v>8421.1769999999997</v>
+      </c>
+      <c r="AA20" s="19">
+        <f t="shared" ref="AA20:AH20" si="203">+Z20*1.03</f>
+        <v>8673.8123099999993</v>
+      </c>
+      <c r="AB20" s="19">
         <f t="shared" si="203"/>
-        <v>13100.313599999998</v>
-      </c>
-      <c r="AC20" s="1">
+        <v>8934.0266792999992</v>
+      </c>
+      <c r="AC20" s="19">
         <f t="shared" si="203"/>
-        <v>15720.376319999996</v>
-      </c>
-      <c r="AD20" s="1">
+        <v>9202.0474796789986</v>
+      </c>
+      <c r="AD20" s="19">
         <f t="shared" si="203"/>
-        <v>18864.451583999995</v>
-      </c>
-      <c r="AE20" s="1">
+        <v>9478.1089040693696</v>
+      </c>
+      <c r="AE20" s="19">
         <f t="shared" si="203"/>
-        <v>22637.341900799995</v>
-      </c>
-      <c r="AF20" s="1">
+        <v>9762.4521711914513</v>
+      </c>
+      <c r="AF20" s="19">
         <f t="shared" si="203"/>
-        <v>27164.810280959991</v>
-      </c>
-      <c r="AG20" s="1">
+        <v>10055.325736327195</v>
+      </c>
+      <c r="AG20" s="19">
         <f t="shared" si="203"/>
-        <v>32597.77233715199</v>
-      </c>
-      <c r="AH20" s="1">
+        <v>10356.98550841701</v>
+      </c>
+      <c r="AH20" s="19">
         <f t="shared" si="203"/>
-        <v>39117.326804582386</v>
-      </c>
-    </row>
-    <row r="21" spans="2:235" s="6" customFormat="1">
+        <v>10667.695073669522</v>
+      </c>
+    </row>
+    <row r="21" spans="1:235" s="6" customFormat="1">
       <c r="B21" s="6" t="s">
         <v>3</v>
       </c>
@@ -2653,20 +2828,14 @@
         <v>942.9</v>
       </c>
       <c r="L21" s="6">
-        <f>+L$20*(K21/K$20)</f>
-        <v>942.9</v>
+        <v>995.5</v>
       </c>
       <c r="M21" s="6">
-        <f t="shared" ref="M21:O24" si="206">+M$20*(L21/L$20)</f>
-        <v>942.9</v>
+        <v>1004.7</v>
       </c>
       <c r="N21" s="6">
-        <f t="shared" si="206"/>
-        <v>942.9</v>
-      </c>
-      <c r="O21" s="6">
-        <f t="shared" si="206"/>
-        <v>0</v>
+        <f t="shared" ref="N21:N24" si="206">+N$20*(M21/M$20)</f>
+        <v>1065.4808387563269</v>
       </c>
       <c r="U21" s="6">
         <v>2398.1999999999998</v>
@@ -2682,46 +2851,46 @@
       </c>
       <c r="Y21" s="1">
         <f t="shared" ref="Y21:Y29" si="207">SUM(K21:N21)</f>
-        <v>3771.6</v>
+        <v>4008.5808387563275</v>
       </c>
       <c r="Z21" s="6">
         <f t="shared" ref="Z21:AH21" si="208">+Z$20*(Y21/Y$20)</f>
-        <v>4525.9199999999992</v>
+        <v>4128.8382639190177</v>
       </c>
       <c r="AA21" s="6">
         <f t="shared" si="208"/>
-        <v>5431.1039999999994</v>
+        <v>4252.7034118365882</v>
       </c>
       <c r="AB21" s="6">
         <f t="shared" si="208"/>
-        <v>6517.3247999999994</v>
+        <v>4380.284514191686</v>
       </c>
       <c r="AC21" s="6">
         <f t="shared" si="208"/>
-        <v>7820.7897599999988</v>
+        <v>4511.6930496174364</v>
       </c>
       <c r="AD21" s="6">
         <f t="shared" si="208"/>
-        <v>9384.9477119999992</v>
+        <v>4647.0438411059595</v>
       </c>
       <c r="AE21" s="6">
         <f t="shared" si="208"/>
-        <v>11261.9372544</v>
+        <v>4786.4551563391387</v>
       </c>
       <c r="AF21" s="6">
         <f t="shared" si="208"/>
-        <v>13514.324705279998</v>
+        <v>4930.0488110293136</v>
       </c>
       <c r="AG21" s="6">
         <f t="shared" si="208"/>
-        <v>16217.189646335999</v>
+        <v>5077.9502753601928</v>
       </c>
       <c r="AH21" s="6">
         <f t="shared" si="208"/>
-        <v>19460.627575603197</v>
-      </c>
-    </row>
-    <row r="22" spans="2:235" s="6" customFormat="1">
+        <v>5230.2887836209993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:235" s="6" customFormat="1">
       <c r="B22" s="6" t="s">
         <v>28</v>
       </c>
@@ -2763,19 +2932,15 @@
       </c>
       <c r="L22" s="6">
         <f>+L20-L21</f>
-        <v>952.4</v>
+        <v>1010.5999999999999</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" ref="M22:O22" si="209">+M20-M21</f>
-        <v>952.4</v>
+        <f t="shared" ref="M22:N22" si="209">+M20-M21</f>
+        <v>1069.8</v>
       </c>
       <c r="N22" s="6">
         <f t="shared" si="209"/>
-        <v>952.4</v>
-      </c>
-      <c r="O22" s="6">
-        <f t="shared" si="209"/>
-        <v>0</v>
+        <v>1134.5191612436731</v>
       </c>
       <c r="U22" s="6">
         <f>+U20-U21</f>
@@ -2795,46 +2960,46 @@
       </c>
       <c r="Y22" s="1">
         <f t="shared" si="207"/>
-        <v>3809.6</v>
+        <v>4167.3191612436731</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" ref="Z22" si="210">+Z20-Z21</f>
-        <v>4571.5199999999995</v>
+        <v>4292.338736080982</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" ref="AA22" si="211">+AA20-AA21</f>
-        <v>5485.8239999999987</v>
+        <v>4421.1088981634111</v>
       </c>
       <c r="AB22" s="6">
         <f t="shared" ref="AB22" si="212">+AB20-AB21</f>
-        <v>6582.9887999999983</v>
+        <v>4553.7421651083132</v>
       </c>
       <c r="AC22" s="6">
         <f t="shared" ref="AC22" si="213">+AC20-AC21</f>
-        <v>7899.586559999997</v>
+        <v>4690.3544300615622</v>
       </c>
       <c r="AD22" s="6">
         <f t="shared" ref="AD22" si="214">+AD20-AD21</f>
-        <v>9479.5038719999957</v>
+        <v>4831.0650629634101</v>
       </c>
       <c r="AE22" s="6">
         <f t="shared" ref="AE22" si="215">+AE20-AE21</f>
-        <v>11375.404646399995</v>
+        <v>4975.9970148523125</v>
       </c>
       <c r="AF22" s="6">
         <f t="shared" ref="AF22" si="216">+AF20-AF21</f>
-        <v>13650.485575679993</v>
+        <v>5125.2769252978815</v>
       </c>
       <c r="AG22" s="6">
         <f t="shared" ref="AG22" si="217">+AG20-AG21</f>
-        <v>16380.582690815991</v>
+        <v>5279.0352330568176</v>
       </c>
       <c r="AH22" s="6">
         <f t="shared" ref="AH22" si="218">+AH20-AH21</f>
-        <v>19656.699228979189</v>
-      </c>
-    </row>
-    <row r="23" spans="2:235">
+        <v>5437.4062900485224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:235">
       <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
@@ -2868,16 +3033,14 @@
         <v>507.7</v>
       </c>
       <c r="L23" s="6">
-        <f>+L$20*(K23/K$20)</f>
-        <v>507.69999999999993</v>
+        <v>519</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="206"/>
-        <v>507.69999999999993</v>
+        <v>512.5</v>
       </c>
       <c r="N23" s="6">
         <f t="shared" si="206"/>
-        <v>507.69999999999993</v>
+        <v>543.50445890576043</v>
       </c>
       <c r="U23" s="1">
         <v>1424.2</v>
@@ -2893,46 +3056,46 @@
       </c>
       <c r="Y23" s="1">
         <f t="shared" si="207"/>
-        <v>2030.7999999999997</v>
+        <v>2082.7044589057605</v>
       </c>
       <c r="Z23" s="6">
         <f t="shared" ref="Z23:AH23" si="219">+Z$20*(Y23/Y$20)</f>
-        <v>2436.9599999999996</v>
+        <v>2145.1855926729336</v>
       </c>
       <c r="AA23" s="6">
         <f t="shared" si="219"/>
-        <v>2924.3519999999994</v>
+        <v>2209.5411604531214</v>
       </c>
       <c r="AB23" s="6">
         <f t="shared" si="219"/>
-        <v>3509.2223999999992</v>
+        <v>2275.827395266715</v>
       </c>
       <c r="AC23" s="6">
         <f t="shared" si="219"/>
-        <v>4211.0668799999985</v>
+        <v>2344.1022171247164</v>
       </c>
       <c r="AD23" s="6">
         <f t="shared" si="219"/>
-        <v>5053.2802559999982</v>
+        <v>2414.425283638458</v>
       </c>
       <c r="AE23" s="6">
         <f t="shared" si="219"/>
-        <v>6063.9363071999978</v>
+        <v>2486.8580421476117</v>
       </c>
       <c r="AF23" s="6">
         <f t="shared" si="219"/>
-        <v>7276.7235686399972</v>
+        <v>2561.4637834120404</v>
       </c>
       <c r="AG23" s="6">
         <f t="shared" si="219"/>
-        <v>8732.0682823679963</v>
+        <v>2638.3076969144013</v>
       </c>
       <c r="AH23" s="6">
         <f t="shared" si="219"/>
-        <v>10478.481938841594</v>
-      </c>
-    </row>
-    <row r="24" spans="2:235">
+        <v>2717.4569278218337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:235">
       <c r="B24" s="1" t="s">
         <v>30</v>
       </c>
@@ -2966,16 +3129,14 @@
         <v>186.4</v>
       </c>
       <c r="L24" s="6">
-        <f>+L$20*(K24/K$20)</f>
-        <v>186.4</v>
+        <v>192.8</v>
       </c>
       <c r="M24" s="6">
-        <f t="shared" si="206"/>
-        <v>186.4</v>
+        <v>189.9</v>
       </c>
       <c r="N24" s="6">
         <f t="shared" si="206"/>
-        <v>186.4</v>
+        <v>201.38828633405643</v>
       </c>
       <c r="U24" s="1">
         <v>955.3</v>
@@ -2991,46 +3152,46 @@
       </c>
       <c r="Y24" s="1">
         <f t="shared" si="207"/>
-        <v>745.6</v>
+        <v>770.48828633405651</v>
       </c>
       <c r="Z24" s="6">
         <f t="shared" ref="Z24:AH24" si="220">+Z$20*(Y24/Y$20)</f>
-        <v>894.71999999999991</v>
+        <v>793.60293492407823</v>
       </c>
       <c r="AA24" s="6">
         <f t="shared" si="220"/>
-        <v>1073.664</v>
+        <v>817.41102297180055</v>
       </c>
       <c r="AB24" s="6">
         <f t="shared" si="220"/>
-        <v>1288.3968</v>
+        <v>841.93335366095448</v>
       </c>
       <c r="AC24" s="6">
         <f t="shared" si="220"/>
-        <v>1546.0761599999998</v>
+        <v>867.19135427078311</v>
       </c>
       <c r="AD24" s="6">
         <f t="shared" si="220"/>
-        <v>1855.2913919999996</v>
+        <v>893.20709489890669</v>
       </c>
       <c r="AE24" s="6">
         <f t="shared" si="220"/>
-        <v>2226.3496703999999</v>
+        <v>920.00330774587394</v>
       </c>
       <c r="AF24" s="6">
         <f t="shared" si="220"/>
-        <v>2671.6196044799999</v>
+        <v>947.60340697825018</v>
       </c>
       <c r="AG24" s="6">
         <f t="shared" si="220"/>
-        <v>3205.9435253759998</v>
+        <v>976.03150918759763</v>
       </c>
       <c r="AH24" s="6">
         <f t="shared" si="220"/>
-        <v>3847.1322304511996</v>
-      </c>
-    </row>
-    <row r="25" spans="2:235">
+        <v>1005.3124544632257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:235">
       <c r="B25" s="1" t="s">
         <v>31</v>
       </c>
@@ -3072,15 +3233,15 @@
       </c>
       <c r="L25" s="1">
         <f t="shared" ref="L25:N25" si="221">+L22-SUM(L23:L24)</f>
-        <v>258.30000000000007</v>
+        <v>298.79999999999995</v>
       </c>
       <c r="M25" s="1">
         <f t="shared" si="221"/>
-        <v>258.30000000000007</v>
+        <v>367.4</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" si="221"/>
-        <v>258.30000000000007</v>
+        <v>389.62641600385632</v>
       </c>
       <c r="U25" s="1">
         <f>+U22-SUM(U23:U24)</f>
@@ -3100,46 +3261,46 @@
       </c>
       <c r="Y25" s="1">
         <f t="shared" si="207"/>
-        <v>1033.2000000000003</v>
+        <v>1314.1264160038563</v>
       </c>
       <c r="Z25" s="1">
         <f t="shared" ref="Z25" si="222">+Z22-SUM(Z23:Z24)</f>
-        <v>1239.8400000000001</v>
+        <v>1353.55020848397</v>
       </c>
       <c r="AA25" s="1">
         <f t="shared" ref="AA25" si="223">+AA22-SUM(AA23:AA24)</f>
-        <v>1487.8079999999991</v>
+        <v>1394.1567147384894</v>
       </c>
       <c r="AB25" s="1">
         <f t="shared" ref="AB25" si="224">+AB22-SUM(AB23:AB24)</f>
-        <v>1785.3695999999991</v>
+        <v>1435.9814161806435</v>
       </c>
       <c r="AC25" s="1">
         <f t="shared" ref="AC25" si="225">+AC22-SUM(AC23:AC24)</f>
-        <v>2142.4435199999989</v>
+        <v>1479.0608586660628</v>
       </c>
       <c r="AD25" s="1">
         <f t="shared" ref="AD25" si="226">+AD22-SUM(AD23:AD24)</f>
-        <v>2570.9322239999983</v>
+        <v>1523.4326844260454</v>
       </c>
       <c r="AE25" s="1">
         <f t="shared" ref="AE25" si="227">+AE22-SUM(AE23:AE24)</f>
-        <v>3085.118668799998</v>
+        <v>1569.135664958827</v>
       </c>
       <c r="AF25" s="1">
         <f t="shared" ref="AF25" si="228">+AF22-SUM(AF23:AF24)</f>
-        <v>3702.1424025599972</v>
+        <v>1616.2097349075912</v>
       </c>
       <c r="AG25" s="1">
         <f t="shared" ref="AG25" si="229">+AG22-SUM(AG23:AG24)</f>
-        <v>4442.5708830719941</v>
+        <v>1664.6960269548185</v>
       </c>
       <c r="AH25" s="1">
         <f t="shared" ref="AH25" si="230">+AH22-SUM(AH23:AH24)</f>
-        <v>5331.0850596863947</v>
-      </c>
-    </row>
-    <row r="26" spans="2:235">
+        <v>1714.6369077634631</v>
+      </c>
+    </row>
+    <row r="26" spans="1:235">
       <c r="B26" s="1" t="s">
         <v>32</v>
       </c>
@@ -3174,16 +3335,16 @@
         <v>-54.7</v>
       </c>
       <c r="L26" s="1">
-        <f>+L25*(K26/K25)</f>
-        <v>-54.700000000000024</v>
+        <f>+-51.9-4.5</f>
+        <v>-56.4</v>
       </c>
       <c r="M26" s="1">
-        <f t="shared" ref="M26:N26" si="231">+M25*(L26/L25)</f>
-        <v>-54.700000000000024</v>
+        <f>+-51.2+1908.8</f>
+        <v>1857.6</v>
       </c>
       <c r="N26" s="1">
-        <f t="shared" si="231"/>
-        <v>-54.700000000000024</v>
+        <f t="shared" ref="N26" si="231">+N25*(M26/M25)</f>
+        <v>1969.9783080260304</v>
       </c>
       <c r="U26" s="1">
         <v>-135.80000000000001</v>
@@ -3201,46 +3362,46 @@
       </c>
       <c r="Y26" s="1">
         <f t="shared" si="207"/>
-        <v>-218.80000000000007</v>
+        <v>3716.4783080260304</v>
       </c>
       <c r="Z26" s="1">
         <f t="shared" ref="Z26" si="232">+Z25*(Y26/Y25)</f>
-        <v>-262.56000000000006</v>
+        <v>3827.9726572668055</v>
       </c>
       <c r="AA26" s="1">
         <f t="shared" ref="AA26" si="233">+AA25*(Z26/Z25)</f>
-        <v>-315.07199999999983</v>
+        <v>3942.8118369848107</v>
       </c>
       <c r="AB26" s="1">
         <f t="shared" ref="AB26" si="234">+AB25*(AA26/AA25)</f>
-        <v>-378.08639999999986</v>
+        <v>4061.0961920943532</v>
       </c>
       <c r="AC26" s="1">
         <f t="shared" ref="AC26" si="235">+AC25*(AB26/AB25)</f>
-        <v>-453.70367999999979</v>
+        <v>4182.929077857184</v>
       </c>
       <c r="AD26" s="1">
         <f t="shared" ref="AD26" si="236">+AD25*(AC26/AC25)</f>
-        <v>-544.44441599999971</v>
+        <v>4308.4169501929009</v>
       </c>
       <c r="AE26" s="1">
         <f t="shared" ref="AE26" si="237">+AE25*(AD26/AD25)</f>
-        <v>-653.3332991999996</v>
+        <v>4437.6694586986887</v>
       </c>
       <c r="AF26" s="1">
         <f t="shared" ref="AF26" si="238">+AF25*(AE26/AE25)</f>
-        <v>-783.99995903999945</v>
+        <v>4570.7995424596475</v>
       </c>
       <c r="AG26" s="1">
         <f t="shared" ref="AG26" si="239">+AG25*(AF26/AF25)</f>
-        <v>-940.79995084799884</v>
+        <v>4707.9235287334359</v>
       </c>
       <c r="AH26" s="1">
         <f t="shared" ref="AH26" si="240">+AH25*(AG26/AG25)</f>
-        <v>-1128.959941017599</v>
-      </c>
-    </row>
-    <row r="27" spans="2:235">
+        <v>4849.1612345954391</v>
+      </c>
+    </row>
+    <row r="27" spans="1:235">
       <c r="B27" s="1" t="s">
         <v>33</v>
       </c>
@@ -3282,15 +3443,15 @@
       </c>
       <c r="L27" s="1">
         <f>+L25+L26</f>
-        <v>203.60000000000005</v>
+        <v>242.39999999999995</v>
       </c>
       <c r="M27" s="1">
         <f t="shared" ref="M27:N27" si="241">+M25+M26</f>
-        <v>203.60000000000005</v>
+        <v>2225</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" si="241"/>
-        <v>203.60000000000005</v>
+        <v>2359.6047240298867</v>
       </c>
       <c r="U27" s="1">
         <f>+U25+U26</f>
@@ -3310,46 +3471,46 @@
       </c>
       <c r="Y27" s="1">
         <f t="shared" si="207"/>
-        <v>814.40000000000009</v>
+        <v>5030.6047240298867</v>
       </c>
       <c r="Z27" s="1">
         <f t="shared" ref="Z27" si="242">+Z25+Z26</f>
-        <v>977.28000000000009</v>
+        <v>5181.522865750776</v>
       </c>
       <c r="AA27" s="1">
         <f t="shared" ref="AA27" si="243">+AA25+AA26</f>
-        <v>1172.7359999999992</v>
+        <v>5336.9685517233002</v>
       </c>
       <c r="AB27" s="1">
         <f t="shared" ref="AB27" si="244">+AB25+AB26</f>
-        <v>1407.2831999999992</v>
+        <v>5497.0776082749962</v>
       </c>
       <c r="AC27" s="1">
         <f t="shared" ref="AC27" si="245">+AC25+AC26</f>
-        <v>1688.739839999999</v>
+        <v>5661.9899365232468</v>
       </c>
       <c r="AD27" s="1">
         <f t="shared" ref="AD27" si="246">+AD25+AD26</f>
-        <v>2026.4878079999985</v>
+        <v>5831.8496346189459</v>
       </c>
       <c r="AE27" s="1">
         <f t="shared" ref="AE27" si="247">+AE25+AE26</f>
-        <v>2431.7853695999984</v>
+        <v>6006.8051236575157</v>
       </c>
       <c r="AF27" s="1">
         <f t="shared" ref="AF27" si="248">+AF25+AF26</f>
-        <v>2918.1424435199979</v>
+        <v>6187.0092773672386</v>
       </c>
       <c r="AG27" s="1">
         <f t="shared" ref="AG27" si="249">+AG25+AG26</f>
-        <v>3501.7709322239953</v>
+        <v>6372.619555688254</v>
       </c>
       <c r="AH27" s="1">
         <f t="shared" ref="AH27" si="250">+AH25+AH26</f>
-        <v>4202.1251186687959</v>
-      </c>
-    </row>
-    <row r="28" spans="2:235">
+        <v>6563.7981423589026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:235">
       <c r="B28" s="1" t="s">
         <v>34</v>
       </c>
@@ -3383,16 +3544,14 @@
         <v>38</v>
       </c>
       <c r="L28" s="1">
-        <f>+L27*(K28/K27)</f>
-        <v>38.000000000000014</v>
+        <v>38.9</v>
       </c>
       <c r="M28" s="1">
-        <f t="shared" ref="M28:N28" si="251">+M27*(L28/L27)</f>
-        <v>38.000000000000014</v>
+        <v>314.10000000000002</v>
       </c>
       <c r="N28" s="1">
-        <f t="shared" si="251"/>
-        <v>38.000000000000014</v>
+        <f t="shared" ref="N28" si="251">+N27*(M28/M27)</f>
+        <v>333.10195227765729</v>
       </c>
       <c r="U28" s="1">
         <v>-62.5</v>
@@ -3408,46 +3567,46 @@
       </c>
       <c r="Y28" s="1">
         <f t="shared" si="207"/>
-        <v>152.00000000000006</v>
+        <v>724.10195227765735</v>
       </c>
       <c r="Z28" s="1">
         <f t="shared" ref="Z28" si="252">+Z27*(Y28/Y27)</f>
-        <v>182.40000000000006</v>
+        <v>745.82501084598596</v>
       </c>
       <c r="AA28" s="1">
         <f t="shared" ref="AA28" si="253">+AA27*(Z28/Z27)</f>
-        <v>218.87999999999991</v>
+        <v>768.19976117136571</v>
       </c>
       <c r="AB28" s="1">
         <f t="shared" ref="AB28" si="254">+AB27*(AA28/AA27)</f>
-        <v>262.65599999999989</v>
+        <v>791.24575400650633</v>
       </c>
       <c r="AC28" s="1">
         <f t="shared" ref="AC28" si="255">+AC27*(AB28/AB27)</f>
-        <v>315.18719999999985</v>
+        <v>814.98312662670151</v>
       </c>
       <c r="AD28" s="1">
         <f t="shared" ref="AD28" si="256">+AD27*(AC28/AC27)</f>
-        <v>378.22463999999979</v>
+        <v>839.43262042550282</v>
       </c>
       <c r="AE28" s="1">
         <f t="shared" ref="AE28" si="257">+AE27*(AD28/AD27)</f>
-        <v>453.86956799999973</v>
+        <v>864.6155990382681</v>
       </c>
       <c r="AF28" s="1">
         <f t="shared" ref="AF28" si="258">+AF27*(AE28/AE27)</f>
-        <v>544.64348159999963</v>
+        <v>890.5540670094158</v>
       </c>
       <c r="AG28" s="1">
         <f t="shared" ref="AG28" si="259">+AG27*(AF28/AF27)</f>
-        <v>653.57217791999915</v>
+        <v>917.27068901969801</v>
       </c>
       <c r="AH28" s="1">
         <f t="shared" ref="AH28" si="260">+AH27*(AG28/AG27)</f>
-        <v>784.28661350399921</v>
-      </c>
-    </row>
-    <row r="29" spans="2:235">
+        <v>944.7888096902891</v>
+      </c>
+    </row>
+    <row r="29" spans="1:235">
       <c r="B29" s="1" t="s">
         <v>35</v>
       </c>
@@ -3489,15 +3648,15 @@
       </c>
       <c r="L29" s="1">
         <f>+L27-L28</f>
-        <v>165.60000000000002</v>
+        <v>203.49999999999994</v>
       </c>
       <c r="M29" s="1">
         <f t="shared" ref="M29:N29" si="261">+M27-M28</f>
-        <v>165.60000000000002</v>
+        <v>1910.9</v>
       </c>
       <c r="N29" s="1">
         <f t="shared" si="261"/>
-        <v>165.60000000000002</v>
+        <v>2026.5027717522294</v>
       </c>
       <c r="U29" s="1">
         <f>+U27-U28</f>
@@ -3517,847 +3676,852 @@
       </c>
       <c r="Y29" s="1">
         <f t="shared" si="207"/>
-        <v>662.40000000000009</v>
+        <v>4306.5027717522298</v>
       </c>
       <c r="Z29" s="1">
         <f t="shared" ref="Z29" si="262">+Z27-Z28</f>
-        <v>794.88</v>
+        <v>4435.6978549047899</v>
       </c>
       <c r="AA29" s="1">
         <f t="shared" ref="AA29" si="263">+AA27-AA28</f>
-        <v>953.85599999999931</v>
+        <v>4568.7687905519342</v>
       </c>
       <c r="AB29" s="1">
         <f t="shared" ref="AB29" si="264">+AB27-AB28</f>
-        <v>1144.6271999999992</v>
+        <v>4705.8318542684901</v>
       </c>
       <c r="AC29" s="1">
         <f t="shared" ref="AC29" si="265">+AC27-AC28</f>
-        <v>1373.5526399999992</v>
+        <v>4847.0068098965457</v>
       </c>
       <c r="AD29" s="1">
         <f t="shared" ref="AD29" si="266">+AD27-AD28</f>
-        <v>1648.2631679999986</v>
+        <v>4992.4170141934428</v>
       </c>
       <c r="AE29" s="1">
         <f t="shared" ref="AE29" si="267">+AE27-AE28</f>
-        <v>1977.9158015999988</v>
+        <v>5142.1895246192471</v>
       </c>
       <c r="AF29" s="1">
         <f t="shared" ref="AF29" si="268">+AF27-AF28</f>
-        <v>2373.4989619199982</v>
+        <v>5296.4552103578226</v>
       </c>
       <c r="AG29" s="1">
         <f t="shared" ref="AG29" si="269">+AG27-AG28</f>
-        <v>2848.1987543039959</v>
+        <v>5455.3488666685562</v>
       </c>
       <c r="AH29" s="1">
         <f t="shared" ref="AH29" si="270">+AH27-AH28</f>
-        <v>3417.8385051647965</v>
+        <v>5619.0093326686138</v>
       </c>
       <c r="AI29" s="1">
         <f>+AH29*(1+$AJ$33)</f>
-        <v>3452.0168902164446</v>
+        <v>5675.1994259952999</v>
       </c>
       <c r="AJ29" s="1">
         <f t="shared" ref="AJ29:CU29" si="271">+AI29*(1+$AJ$33)</f>
-        <v>3486.5370591186092</v>
+        <v>5731.9514202552527</v>
       </c>
       <c r="AK29" s="1">
         <f t="shared" si="271"/>
-        <v>3521.4024297097953</v>
+        <v>5789.2709344578052</v>
       </c>
       <c r="AL29" s="1">
         <f t="shared" si="271"/>
-        <v>3556.6164540068935</v>
+        <v>5847.1636438023834</v>
       </c>
       <c r="AM29" s="1">
         <f t="shared" si="271"/>
-        <v>3592.1826185469627</v>
+        <v>5905.6352802404072</v>
       </c>
       <c r="AN29" s="1">
         <f t="shared" si="271"/>
-        <v>3628.1044447324325</v>
+        <v>5964.6916330428112</v>
       </c>
       <c r="AO29" s="1">
         <f t="shared" si="271"/>
-        <v>3664.3854891797569</v>
+        <v>6024.3385493732394</v>
       </c>
       <c r="AP29" s="1">
         <f t="shared" si="271"/>
-        <v>3701.0293440715545</v>
+        <v>6084.581934866972</v>
       </c>
       <c r="AQ29" s="1">
         <f t="shared" si="271"/>
-        <v>3738.03963751227</v>
+        <v>6145.4277542156415</v>
       </c>
       <c r="AR29" s="1">
         <f t="shared" si="271"/>
-        <v>3775.4200338873929</v>
+        <v>6206.8820317577984</v>
       </c>
       <c r="AS29" s="1">
         <f t="shared" si="271"/>
-        <v>3813.1742342262669</v>
+        <v>6268.9508520753761</v>
       </c>
       <c r="AT29" s="1">
         <f t="shared" si="271"/>
-        <v>3851.3059765685298</v>
+        <v>6331.6403605961295</v>
       </c>
       <c r="AU29" s="1">
         <f t="shared" si="271"/>
-        <v>3889.8190363342151</v>
+        <v>6394.9567642020911</v>
       </c>
       <c r="AV29" s="1">
         <f t="shared" si="271"/>
-        <v>3928.7172266975572</v>
+        <v>6458.9063318441122</v>
       </c>
       <c r="AW29" s="1">
         <f t="shared" si="271"/>
-        <v>3968.0043989645328</v>
+        <v>6523.495395162553</v>
       </c>
       <c r="AX29" s="1">
         <f t="shared" si="271"/>
-        <v>4007.6844429541784</v>
+        <v>6588.7303491141784</v>
       </c>
       <c r="AY29" s="1">
         <f t="shared" si="271"/>
-        <v>4047.7612873837202</v>
+        <v>6654.6176526053205</v>
       </c>
       <c r="AZ29" s="1">
         <f t="shared" si="271"/>
-        <v>4088.2389002575574</v>
+        <v>6721.1638291313739</v>
       </c>
       <c r="BA29" s="1">
         <f t="shared" si="271"/>
-        <v>4129.1212892601334</v>
+        <v>6788.3754674226875</v>
       </c>
       <c r="BB29" s="1">
         <f t="shared" si="271"/>
-        <v>4170.4125021527343</v>
+        <v>6856.2592220969145</v>
       </c>
       <c r="BC29" s="1">
         <f t="shared" si="271"/>
-        <v>4212.1166271742613</v>
+        <v>6924.8218143178838</v>
       </c>
       <c r="BD29" s="1">
         <f t="shared" si="271"/>
-        <v>4254.2377934460037</v>
+        <v>6994.0700324610625</v>
       </c>
       <c r="BE29" s="1">
         <f t="shared" si="271"/>
-        <v>4296.7801713804638</v>
+        <v>7064.0107327856731</v>
       </c>
       <c r="BF29" s="1">
         <f t="shared" si="271"/>
-        <v>4339.7479730942687</v>
+        <v>7134.6508401135297</v>
       </c>
       <c r="BG29" s="1">
         <f t="shared" si="271"/>
-        <v>4383.1454528252116</v>
+        <v>7205.9973485146647</v>
       </c>
       <c r="BH29" s="1">
         <f t="shared" si="271"/>
-        <v>4426.9769073534635</v>
+        <v>7278.0573219998114</v>
       </c>
       <c r="BI29" s="1">
         <f t="shared" si="271"/>
-        <v>4471.2466764269984</v>
+        <v>7350.83789521981</v>
       </c>
       <c r="BJ29" s="1">
         <f t="shared" si="271"/>
-        <v>4515.9591431912686</v>
+        <v>7424.3462741720077</v>
       </c>
       <c r="BK29" s="1">
         <f t="shared" si="271"/>
-        <v>4561.1187346231809</v>
+        <v>7498.5897369137283</v>
       </c>
       <c r="BL29" s="1">
         <f t="shared" si="271"/>
-        <v>4606.7299219694123</v>
+        <v>7573.5756342828654</v>
       </c>
       <c r="BM29" s="1">
         <f t="shared" si="271"/>
-        <v>4652.7972211891065</v>
+        <v>7649.311390625694</v>
       </c>
       <c r="BN29" s="1">
         <f t="shared" si="271"/>
-        <v>4699.3251934009977</v>
+        <v>7725.8045045319514</v>
       </c>
       <c r="BO29" s="1">
         <f t="shared" si="271"/>
-        <v>4746.3184453350077</v>
+        <v>7803.0625495772711</v>
       </c>
       <c r="BP29" s="1">
         <f t="shared" si="271"/>
-        <v>4793.7816297883583</v>
+        <v>7881.0931750730442</v>
       </c>
       <c r="BQ29" s="1">
         <f t="shared" si="271"/>
-        <v>4841.719446086242</v>
+        <v>7959.9041068237748</v>
       </c>
       <c r="BR29" s="1">
         <f t="shared" si="271"/>
-        <v>4890.1366405471044</v>
+        <v>8039.5031478920127</v>
       </c>
       <c r="BS29" s="1">
         <f t="shared" si="271"/>
-        <v>4939.0380069525754</v>
+        <v>8119.8981793709327</v>
       </c>
       <c r="BT29" s="1">
         <f t="shared" si="271"/>
-        <v>4988.4283870221016</v>
+        <v>8201.0971611646419</v>
       </c>
       <c r="BU29" s="1">
         <f t="shared" si="271"/>
-        <v>5038.3126708923228</v>
+        <v>8283.1081327762877</v>
       </c>
       <c r="BV29" s="1">
         <f t="shared" si="271"/>
-        <v>5088.6957976012463</v>
+        <v>8365.9392141040498</v>
       </c>
       <c r="BW29" s="1">
         <f t="shared" si="271"/>
-        <v>5139.5827555772585</v>
+        <v>8449.5986062450902</v>
       </c>
       <c r="BX29" s="1">
         <f t="shared" si="271"/>
-        <v>5190.978583133031</v>
+        <v>8534.0945923075415</v>
       </c>
       <c r="BY29" s="1">
         <f t="shared" si="271"/>
-        <v>5242.8883689643617</v>
+        <v>8619.4355382306167</v>
       </c>
       <c r="BZ29" s="1">
         <f t="shared" si="271"/>
-        <v>5295.3172526540056</v>
+        <v>8705.6298936129224</v>
       </c>
       <c r="CA29" s="1">
         <f t="shared" si="271"/>
-        <v>5348.2704251805453</v>
+        <v>8792.6861925490521</v>
       </c>
       <c r="CB29" s="1">
         <f t="shared" si="271"/>
-        <v>5401.7531294323508</v>
+        <v>8880.6130544745429</v>
       </c>
       <c r="CC29" s="1">
         <f t="shared" si="271"/>
-        <v>5455.7706607266746</v>
+        <v>8969.4191850192892</v>
       </c>
       <c r="CD29" s="1">
         <f t="shared" si="271"/>
-        <v>5510.3283673339411</v>
+        <v>9059.1133768694817</v>
       </c>
       <c r="CE29" s="1">
         <f t="shared" si="271"/>
-        <v>5565.4316510072804</v>
+        <v>9149.7045106381775</v>
       </c>
       <c r="CF29" s="1">
         <f t="shared" si="271"/>
-        <v>5621.0859675173533</v>
+        <v>9241.2015557445593</v>
       </c>
       <c r="CG29" s="1">
         <f t="shared" si="271"/>
-        <v>5677.2968271925265</v>
+        <v>9333.6135713020049</v>
       </c>
       <c r="CH29" s="1">
         <f t="shared" si="271"/>
-        <v>5734.069795464452</v>
+        <v>9426.9497070150246</v>
       </c>
       <c r="CI29" s="1">
         <f t="shared" si="271"/>
-        <v>5791.4104934190964</v>
+        <v>9521.2192040851751</v>
       </c>
       <c r="CJ29" s="1">
         <f t="shared" si="271"/>
-        <v>5849.324598353287</v>
+        <v>9616.4313961260268</v>
       </c>
       <c r="CK29" s="1">
         <f t="shared" si="271"/>
-        <v>5907.8178443368197</v>
+        <v>9712.5957100872874</v>
       </c>
       <c r="CL29" s="1">
         <f t="shared" si="271"/>
-        <v>5966.8960227801881</v>
+        <v>9809.7216671881597</v>
       </c>
       <c r="CM29" s="1">
         <f t="shared" si="271"/>
-        <v>6026.5649830079901</v>
+        <v>9907.8188838600418</v>
       </c>
       <c r="CN29" s="1">
         <f t="shared" si="271"/>
-        <v>6086.8306328380704</v>
+        <v>10006.897072698643</v>
       </c>
       <c r="CO29" s="1">
         <f t="shared" si="271"/>
-        <v>6147.6989391664511</v>
+        <v>10106.966043425629</v>
       </c>
       <c r="CP29" s="1">
         <f t="shared" si="271"/>
-        <v>6209.1759285581156</v>
+        <v>10208.035703859885</v>
       </c>
       <c r="CQ29" s="1">
         <f t="shared" si="271"/>
-        <v>6271.2676878436969</v>
+        <v>10310.116060898485</v>
       </c>
       <c r="CR29" s="1">
         <f t="shared" si="271"/>
-        <v>6333.9803647221343</v>
+        <v>10413.21722150747</v>
       </c>
       <c r="CS29" s="1">
         <f t="shared" si="271"/>
-        <v>6397.320168369356</v>
+        <v>10517.349393722545</v>
       </c>
       <c r="CT29" s="1">
         <f t="shared" si="271"/>
-        <v>6461.2933700530493</v>
+        <v>10622.52288765977</v>
       </c>
       <c r="CU29" s="1">
         <f t="shared" si="271"/>
-        <v>6525.9063037535798</v>
+        <v>10728.748116536368</v>
       </c>
       <c r="CV29" s="1">
         <f t="shared" ref="CV29:FE29" si="272">+CU29*(1+$AJ$33)</f>
-        <v>6591.165366791116</v>
+        <v>10836.035597701732</v>
       </c>
       <c r="CW29" s="1">
         <f t="shared" si="272"/>
-        <v>6657.0770204590272</v>
+        <v>10944.39595367875</v>
       </c>
       <c r="CX29" s="1">
         <f t="shared" si="272"/>
-        <v>6723.6477906636173</v>
+        <v>11053.839913215537</v>
       </c>
       <c r="CY29" s="1">
         <f t="shared" si="272"/>
-        <v>6790.8842685702539</v>
+        <v>11164.378312347693</v>
       </c>
       <c r="CZ29" s="1">
         <f t="shared" si="272"/>
-        <v>6858.7931112559563</v>
+        <v>11276.022095471169</v>
       </c>
       <c r="DA29" s="1">
         <f t="shared" si="272"/>
-        <v>6927.3810423685163</v>
+        <v>11388.782316425881</v>
       </c>
       <c r="DB29" s="1">
         <f t="shared" si="272"/>
-        <v>6996.6548527922014</v>
+        <v>11502.67013959014</v>
       </c>
       <c r="DC29" s="1">
         <f t="shared" si="272"/>
-        <v>7066.6214013201234</v>
+        <v>11617.696840986042</v>
       </c>
       <c r="DD29" s="1">
         <f t="shared" si="272"/>
-        <v>7137.2876153333245</v>
+        <v>11733.873809395902</v>
       </c>
       <c r="DE29" s="1">
         <f t="shared" si="272"/>
-        <v>7208.6604914866575</v>
+        <v>11851.21254748986</v>
       </c>
       <c r="DF29" s="1">
         <f t="shared" si="272"/>
-        <v>7280.7470964015238</v>
+        <v>11969.72467296476</v>
       </c>
       <c r="DG29" s="1">
         <f t="shared" si="272"/>
-        <v>7353.5545673655388</v>
+        <v>12089.421919694407</v>
       </c>
       <c r="DH29" s="1">
         <f t="shared" si="272"/>
-        <v>7427.090113039194</v>
+        <v>12210.31613889135</v>
       </c>
       <c r="DI29" s="1">
         <f t="shared" si="272"/>
-        <v>7501.3610141695863</v>
+        <v>12332.419300280264</v>
       </c>
       <c r="DJ29" s="1">
         <f t="shared" si="272"/>
-        <v>7576.3746243112819</v>
+        <v>12455.743493283067</v>
       </c>
       <c r="DK29" s="1">
         <f t="shared" si="272"/>
-        <v>7652.1383705543949</v>
+        <v>12580.300928215898</v>
       </c>
       <c r="DL29" s="1">
         <f t="shared" si="272"/>
-        <v>7728.6597542599393</v>
+        <v>12706.103937498057</v>
       </c>
       <c r="DM29" s="1">
         <f t="shared" si="272"/>
-        <v>7805.9463518025386</v>
+        <v>12833.164976873039</v>
       </c>
       <c r="DN29" s="1">
         <f t="shared" si="272"/>
-        <v>7884.0058153205637</v>
+        <v>12961.496626641769</v>
       </c>
       <c r="DO29" s="1">
         <f t="shared" si="272"/>
-        <v>7962.8458734737696</v>
+        <v>13091.111592908186</v>
       </c>
       <c r="DP29" s="1">
         <f t="shared" si="272"/>
-        <v>8042.4743322085078</v>
+        <v>13222.022708837269</v>
       </c>
       <c r="DQ29" s="1">
         <f t="shared" si="272"/>
-        <v>8122.8990755305931</v>
+        <v>13354.242935925642</v>
       </c>
       <c r="DR29" s="1">
         <f t="shared" si="272"/>
-        <v>8204.128066285899</v>
+        <v>13487.785365284899</v>
       </c>
       <c r="DS29" s="1">
         <f t="shared" si="272"/>
-        <v>8286.1693469487582</v>
+        <v>13622.663218937749</v>
       </c>
       <c r="DT29" s="1">
         <f t="shared" si="272"/>
-        <v>8369.0310404182455</v>
+        <v>13758.889851127127</v>
       </c>
       <c r="DU29" s="1">
         <f t="shared" si="272"/>
-        <v>8452.7213508224286</v>
+        <v>13896.478749638398</v>
       </c>
       <c r="DV29" s="1">
         <f t="shared" si="272"/>
-        <v>8537.2485643306536</v>
+        <v>14035.443537134783</v>
       </c>
       <c r="DW29" s="1">
         <f t="shared" si="272"/>
-        <v>8622.6210499739609</v>
+        <v>14175.79797250613</v>
       </c>
       <c r="DX29" s="1">
         <f t="shared" si="272"/>
-        <v>8708.8472604736999</v>
+        <v>14317.555952231192</v>
       </c>
       <c r="DY29" s="1">
         <f t="shared" si="272"/>
-        <v>8795.9357330784369</v>
+        <v>14460.731511753504</v>
       </c>
       <c r="DZ29" s="1">
         <f t="shared" si="272"/>
-        <v>8883.8950904092217</v>
+        <v>14605.338826871039</v>
       </c>
       <c r="EA29" s="1">
         <f t="shared" si="272"/>
-        <v>8972.7340413133134</v>
+        <v>14751.392215139749</v>
       </c>
       <c r="EB29" s="1">
         <f t="shared" si="272"/>
-        <v>9062.4613817264471</v>
+        <v>14898.906137291147</v>
       </c>
       <c r="EC29" s="1">
         <f t="shared" si="272"/>
-        <v>9153.0859955437118</v>
+        <v>15047.895198664059</v>
       </c>
       <c r="ED29" s="1">
         <f t="shared" si="272"/>
-        <v>9244.6168554991491</v>
+        <v>15198.374150650699</v>
       </c>
       <c r="EE29" s="1">
         <f t="shared" si="272"/>
-        <v>9337.0630240541414</v>
+        <v>15350.357892157206</v>
       </c>
       <c r="EF29" s="1">
         <f t="shared" si="272"/>
-        <v>9430.4336542946821</v>
+        <v>15503.861471078779</v>
       </c>
       <c r="EG29" s="1">
         <f t="shared" si="272"/>
-        <v>9524.7379908376297</v>
+        <v>15658.900085789566</v>
       </c>
       <c r="EH29" s="1">
         <f t="shared" si="272"/>
-        <v>9619.9853707460061</v>
+        <v>15815.489086647462</v>
       </c>
       <c r="EI29" s="1">
         <f t="shared" si="272"/>
-        <v>9716.1852244534657</v>
+        <v>15973.643977513937</v>
       </c>
       <c r="EJ29" s="1">
         <f t="shared" si="272"/>
-        <v>9813.3470766980008</v>
+        <v>16133.380417289076</v>
       </c>
       <c r="EK29" s="1">
         <f t="shared" si="272"/>
-        <v>9911.4805474649802</v>
+        <v>16294.714221461967</v>
       </c>
       <c r="EL29" s="1">
         <f t="shared" si="272"/>
-        <v>10010.59535293963</v>
+        <v>16457.661363676587</v>
       </c>
       <c r="EM29" s="1">
         <f t="shared" si="272"/>
-        <v>10110.701306469027</v>
+        <v>16622.237977313354</v>
       </c>
       <c r="EN29" s="1">
         <f t="shared" si="272"/>
-        <v>10211.808319533717</v>
+        <v>16788.460357086489</v>
       </c>
       <c r="EO29" s="1">
         <f t="shared" si="272"/>
-        <v>10313.926402729054</v>
+        <v>16956.344960657356</v>
       </c>
       <c r="EP29" s="1">
         <f t="shared" si="272"/>
-        <v>10417.065666756343</v>
+        <v>17125.908410263928</v>
       </c>
       <c r="EQ29" s="1">
         <f t="shared" si="272"/>
-        <v>10521.236323423907</v>
+        <v>17297.167494366568</v>
       </c>
       <c r="ER29" s="1">
         <f t="shared" si="272"/>
-        <v>10626.448686658146</v>
+        <v>17470.139169310234</v>
       </c>
       <c r="ES29" s="1">
         <f t="shared" si="272"/>
-        <v>10732.713173524728</v>
+        <v>17644.840561003337</v>
       </c>
       <c r="ET29" s="1">
         <f t="shared" si="272"/>
-        <v>10840.040305259976</v>
+        <v>17821.288966613371</v>
       </c>
       <c r="EU29" s="1">
         <f t="shared" si="272"/>
-        <v>10948.440708312575</v>
+        <v>17999.501856279505</v>
       </c>
       <c r="EV29" s="1">
         <f t="shared" si="272"/>
-        <v>11057.925115395701</v>
+        <v>18179.496874842302</v>
       </c>
       <c r="EW29" s="1">
         <f t="shared" si="272"/>
-        <v>11168.504366549658</v>
+        <v>18361.291843590723</v>
       </c>
       <c r="EX29" s="1">
         <f t="shared" si="272"/>
-        <v>11280.189410215155</v>
+        <v>18544.904762026632</v>
       </c>
       <c r="EY29" s="1">
         <f t="shared" si="272"/>
-        <v>11392.991304317306</v>
+        <v>18730.353809646898</v>
       </c>
       <c r="EZ29" s="1">
         <f t="shared" si="272"/>
-        <v>11506.921217360479</v>
+        <v>18917.657347743367</v>
       </c>
       <c r="FA29" s="1">
         <f t="shared" si="272"/>
-        <v>11621.990429534084</v>
+        <v>19106.833921220801</v>
       </c>
       <c r="FB29" s="1">
         <f t="shared" si="272"/>
-        <v>11738.210333829426</v>
+        <v>19297.902260433009</v>
       </c>
       <c r="FC29" s="1">
         <f t="shared" si="272"/>
-        <v>11855.592437167719</v>
+        <v>19490.881283037339</v>
       </c>
       <c r="FD29" s="1">
         <f t="shared" si="272"/>
-        <v>11974.148361539397</v>
+        <v>19685.790095867713</v>
       </c>
       <c r="FE29" s="1">
         <f t="shared" si="272"/>
-        <v>12093.889845154792</v>
+        <v>19882.647996826388</v>
       </c>
       <c r="FF29" s="1">
         <f t="shared" ref="FF29:HQ29" si="273">+FE29*(1+$AJ$33)</f>
-        <v>12214.82874360634</v>
+        <v>20081.474476794654</v>
       </c>
       <c r="FG29" s="1">
         <f t="shared" si="273"/>
-        <v>12336.977031042403</v>
+        <v>20282.289221562602</v>
       </c>
       <c r="FH29" s="1">
         <f t="shared" si="273"/>
-        <v>12460.346801352827</v>
+        <v>20485.112113778228</v>
       </c>
       <c r="FI29" s="1">
         <f t="shared" si="273"/>
-        <v>12584.950269366356</v>
+        <v>20689.963234916009</v>
       </c>
       <c r="FJ29" s="1">
         <f t="shared" si="273"/>
-        <v>12710.79977206002</v>
+        <v>20896.862867265168</v>
       </c>
       <c r="FK29" s="1">
         <f t="shared" si="273"/>
-        <v>12837.907769780621</v>
+        <v>21105.831495937819</v>
       </c>
       <c r="FL29" s="1">
         <f t="shared" si="273"/>
-        <v>12966.286847478426</v>
+        <v>21316.889810897195</v>
       </c>
       <c r="FM29" s="1">
         <f t="shared" si="273"/>
-        <v>13095.949715953211</v>
+        <v>21530.058709006167</v>
       </c>
       <c r="FN29" s="1">
         <f t="shared" si="273"/>
-        <v>13226.909213112744</v>
+        <v>21745.359296096231</v>
       </c>
       <c r="FO29" s="1">
         <f t="shared" si="273"/>
-        <v>13359.178305243871</v>
+        <v>21962.812889057193</v>
       </c>
       <c r="FP29" s="1">
         <f t="shared" si="273"/>
-        <v>13492.770088296311</v>
+        <v>22182.441017947767</v>
       </c>
       <c r="FQ29" s="1">
         <f t="shared" si="273"/>
-        <v>13627.697789179274</v>
+        <v>22404.265428127244</v>
       </c>
       <c r="FR29" s="1">
         <f t="shared" si="273"/>
-        <v>13763.974767071068</v>
+        <v>22628.308082408515</v>
       </c>
       <c r="FS29" s="1">
         <f t="shared" si="273"/>
-        <v>13901.614514741779</v>
+        <v>22854.591163232602</v>
       </c>
       <c r="FT29" s="1">
         <f t="shared" si="273"/>
-        <v>14040.630659889197</v>
+        <v>23083.137074864928</v>
       </c>
       <c r="FU29" s="1">
         <f t="shared" si="273"/>
-        <v>14181.036966488089</v>
+        <v>23313.968445613576</v>
       </c>
       <c r="FV29" s="1">
         <f t="shared" si="273"/>
-        <v>14322.84733615297</v>
+        <v>23547.108130069711</v>
       </c>
       <c r="FW29" s="1">
         <f t="shared" si="273"/>
-        <v>14466.075809514501</v>
+        <v>23782.579211370408</v>
       </c>
       <c r="FX29" s="1">
         <f t="shared" si="273"/>
-        <v>14610.736567609647</v>
+        <v>24020.405003484113</v>
       </c>
       <c r="FY29" s="1">
         <f t="shared" si="273"/>
-        <v>14756.843933285743</v>
+        <v>24260.609053518954</v>
       </c>
       <c r="FZ29" s="1">
         <f t="shared" si="273"/>
-        <v>14904.412372618601</v>
+        <v>24503.215144054146</v>
       </c>
       <c r="GA29" s="1">
         <f t="shared" si="273"/>
-        <v>15053.456496344787</v>
+        <v>24748.247295494686</v>
       </c>
       <c r="GB29" s="1">
         <f t="shared" si="273"/>
-        <v>15203.991061308234</v>
+        <v>24995.729768449633</v>
       </c>
       <c r="GC29" s="1">
         <f t="shared" si="273"/>
-        <v>15356.030971921316</v>
+        <v>25245.687066134131</v>
       </c>
       <c r="GD29" s="1">
         <f t="shared" si="273"/>
-        <v>15509.591281640529</v>
+        <v>25498.143936795474</v>
       </c>
       <c r="GE29" s="1">
         <f t="shared" si="273"/>
-        <v>15664.687194456934</v>
+        <v>25753.125376163429</v>
       </c>
       <c r="GF29" s="1">
         <f t="shared" si="273"/>
-        <v>15821.334066401503</v>
+        <v>26010.656629925063</v>
       </c>
       <c r="GG29" s="1">
         <f t="shared" si="273"/>
-        <v>15979.547407065518</v>
+        <v>26270.763196224314</v>
       </c>
       <c r="GH29" s="1">
         <f t="shared" si="273"/>
-        <v>16139.342881136174</v>
+        <v>26533.470828186557</v>
       </c>
       <c r="GI29" s="1">
         <f t="shared" si="273"/>
-        <v>16300.736309947535</v>
+        <v>26798.805536468422</v>
       </c>
       <c r="GJ29" s="1">
         <f t="shared" si="273"/>
-        <v>16463.743673047011</v>
+        <v>27066.793591833106</v>
       </c>
       <c r="GK29" s="1">
         <f t="shared" si="273"/>
-        <v>16628.381109777481</v>
+        <v>27337.461527751439</v>
       </c>
       <c r="GL29" s="1">
         <f t="shared" si="273"/>
-        <v>16794.664920875257</v>
+        <v>27610.836143028951</v>
       </c>
       <c r="GM29" s="1">
         <f t="shared" si="273"/>
-        <v>16962.611570084009</v>
+        <v>27886.944504459243</v>
       </c>
       <c r="GN29" s="1">
         <f t="shared" si="273"/>
-        <v>17132.23768578485</v>
+        <v>28165.813949503834</v>
       </c>
       <c r="GO29" s="1">
         <f t="shared" si="273"/>
-        <v>17303.5600626427</v>
+        <v>28447.472088998871</v>
       </c>
       <c r="GP29" s="1">
         <f t="shared" si="273"/>
-        <v>17476.595663269127</v>
+        <v>28731.946809888861</v>
       </c>
       <c r="GQ29" s="1">
         <f t="shared" si="273"/>
-        <v>17651.361619901818</v>
+        <v>29019.26627798775</v>
       </c>
       <c r="GR29" s="1">
         <f t="shared" si="273"/>
-        <v>17827.875236100837</v>
+        <v>29309.458940767629</v>
       </c>
       <c r="GS29" s="1">
         <f t="shared" si="273"/>
-        <v>18006.153988461847</v>
+        <v>29602.553530175304</v>
       </c>
       <c r="GT29" s="1">
         <f t="shared" si="273"/>
-        <v>18186.215528346467</v>
+        <v>29898.579065477057</v>
       </c>
       <c r="GU29" s="1">
         <f t="shared" si="273"/>
-        <v>18368.077683629934</v>
+        <v>30197.564856131827</v>
       </c>
       <c r="GV29" s="1">
         <f t="shared" si="273"/>
-        <v>18551.758460466233</v>
+        <v>30499.540504693145</v>
       </c>
       <c r="GW29" s="1">
         <f t="shared" si="273"/>
-        <v>18737.276045070896</v>
+        <v>30804.535909740076</v>
       </c>
       <c r="GX29" s="1">
         <f t="shared" si="273"/>
-        <v>18924.648805521603</v>
+        <v>31112.581268837475</v>
       </c>
       <c r="GY29" s="1">
         <f t="shared" si="273"/>
-        <v>19113.895293576821</v>
+        <v>31423.707081525852</v>
       </c>
       <c r="GZ29" s="1">
         <f t="shared" si="273"/>
-        <v>19305.03424651259</v>
+        <v>31737.944152341111</v>
       </c>
       <c r="HA29" s="1">
         <f t="shared" si="273"/>
-        <v>19498.084588977716</v>
+        <v>32055.323593864523</v>
       </c>
       <c r="HB29" s="1">
         <f t="shared" si="273"/>
-        <v>19693.065434867494</v>
+        <v>32375.876829803168</v>
       </c>
       <c r="HC29" s="1">
         <f t="shared" si="273"/>
-        <v>19889.996089216169</v>
+        <v>32699.635598101198</v>
       </c>
       <c r="HD29" s="1">
         <f t="shared" si="273"/>
-        <v>20088.896050108331</v>
+        <v>33026.631954082208</v>
       </c>
       <c r="HE29" s="1">
         <f t="shared" si="273"/>
-        <v>20289.785010609416</v>
+        <v>33356.898273623032</v>
       </c>
       <c r="HF29" s="1">
         <f t="shared" si="273"/>
-        <v>20492.682860715511</v>
+        <v>33690.467256359261</v>
       </c>
       <c r="HG29" s="1">
         <f t="shared" si="273"/>
-        <v>20697.609689322668</v>
+        <v>34027.371928922854</v>
       </c>
       <c r="HH29" s="1">
         <f t="shared" si="273"/>
-        <v>20904.585786215895</v>
+        <v>34367.645648212085</v>
       </c>
       <c r="HI29" s="1">
         <f t="shared" si="273"/>
-        <v>21113.631644078054</v>
+        <v>34711.322104694205</v>
       </c>
       <c r="HJ29" s="1">
         <f t="shared" si="273"/>
-        <v>21324.767960518835</v>
+        <v>35058.435325741149</v>
       </c>
       <c r="HK29" s="1">
         <f t="shared" si="273"/>
-        <v>21538.015640124024</v>
+        <v>35409.019678998564</v>
       </c>
       <c r="HL29" s="1">
         <f t="shared" si="273"/>
-        <v>21753.395796525263</v>
+        <v>35763.109875788548</v>
       </c>
       <c r="HM29" s="1">
         <f t="shared" si="273"/>
-        <v>21970.929754490517</v>
+        <v>36120.740974546432</v>
       </c>
       <c r="HN29" s="1">
         <f t="shared" si="273"/>
-        <v>22190.639052035422</v>
+        <v>36481.9483842919</v>
       </c>
       <c r="HO29" s="1">
         <f t="shared" si="273"/>
-        <v>22412.545442555776</v>
+        <v>36846.767868134819</v>
       </c>
       <c r="HP29" s="1">
         <f t="shared" si="273"/>
-        <v>22636.670896981333</v>
+        <v>37215.23554681617</v>
       </c>
       <c r="HQ29" s="1">
         <f t="shared" si="273"/>
-        <v>22863.037605951147</v>
+        <v>37587.387902284332</v>
       </c>
       <c r="HR29" s="1">
         <f t="shared" ref="HR29:HW29" si="274">+HQ29*(1+$AJ$33)</f>
-        <v>23091.667982010658</v>
+        <v>37963.261781307177</v>
       </c>
       <c r="HS29" s="1">
         <f t="shared" si="274"/>
-        <v>23322.584661830766</v>
+        <v>38342.894399120247</v>
       </c>
       <c r="HT29" s="1">
         <f t="shared" si="274"/>
-        <v>23555.810508449074</v>
+        <v>38726.32334311145</v>
       </c>
       <c r="HU29" s="1">
         <f t="shared" si="274"/>
-        <v>23791.368613533567</v>
+        <v>39113.586576542562</v>
       </c>
       <c r="HV29" s="1">
         <f t="shared" si="274"/>
-        <v>24029.282299668903</v>
+        <v>39504.72244230799</v>
       </c>
       <c r="HW29" s="1">
         <f t="shared" si="274"/>
-        <v>24269.575122665592</v>
+        <v>39899.769666731067</v>
       </c>
       <c r="HX29" s="1">
         <f t="shared" ref="HX29:IA29" si="275">+HW29*(1+$AJ$33)</f>
-        <v>24512.270873892248</v>
+        <v>40298.76736339838</v>
       </c>
       <c r="HY29" s="1">
         <f t="shared" si="275"/>
-        <v>24757.393582631172</v>
+        <v>40701.755037032366</v>
       </c>
       <c r="HZ29" s="1">
         <f t="shared" si="275"/>
-        <v>25004.967518457484</v>
+        <v>41108.772587402687</v>
       </c>
       <c r="IA29" s="1">
         <f t="shared" si="275"/>
-        <v>25255.017193642059</v>
+        <v>41519.860313276717</v>
+      </c>
+    </row>
+    <row r="32" spans="1:235">
+      <c r="B32" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="2:36" s="4" customFormat="1">
@@ -4365,7 +4529,7 @@
         <v>21</v>
       </c>
       <c r="G33" s="8">
-        <f t="shared" ref="G33:K33" si="276">+G15/C15-1</f>
+        <f t="shared" ref="G33:M33" si="276">+G15/C15-1</f>
         <v>0.87333639284075248</v>
       </c>
       <c r="H33" s="8">
@@ -4384,6 +4548,14 @@
         <f t="shared" si="276"/>
         <v>0.76457618814306705</v>
       </c>
+      <c r="L33" s="8">
+        <f t="shared" si="276"/>
+        <v>0.69201952548529921</v>
+      </c>
+      <c r="M33" s="8">
+        <f t="shared" si="276"/>
+        <v>0.37853056034874233</v>
+      </c>
       <c r="T33" s="4">
         <f t="shared" ref="T33" si="277">+T15/S15-1</f>
         <v>0.26335057371507364</v>
@@ -4405,7 +4577,7 @@
         <v>0.87855821716966664</v>
       </c>
       <c r="AI33" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AJ33" s="4">
         <v>0.01</v>
@@ -4435,6 +4607,14 @@
         <f>+K16/G16-1</f>
         <v>0.15937295885042468</v>
       </c>
+      <c r="L34" s="4">
+        <f>+L16/H16-1</f>
+        <v>0.28211920529801326</v>
+      </c>
+      <c r="M34" s="4">
+        <f>+M16/I16-1</f>
+        <v>0.57190192180251809</v>
+      </c>
       <c r="T34" s="4">
         <f t="shared" ref="T34" si="280">+T16/S16-1</f>
         <v>0.71937896896737241</v>
@@ -4456,10 +4636,10 @@
         <v>-0.49006838163464672</v>
       </c>
       <c r="AI34" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AJ34" s="4">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="35" spans="2:36" s="4" customFormat="1">
@@ -4467,7 +4647,7 @@
         <v>26</v>
       </c>
       <c r="G35" s="4">
-        <f t="shared" ref="G35:K35" si="282">+G17/C17-1</f>
+        <f t="shared" ref="G35:M35" si="282">+G17/C17-1</f>
         <v>-0.75232838909968958</v>
       </c>
       <c r="H35" s="4">
@@ -4486,6 +4666,14 @@
         <f t="shared" si="282"/>
         <v>0.9275766016713094</v>
       </c>
+      <c r="L35" s="4">
+        <f t="shared" si="282"/>
+        <v>0.71409749670619216</v>
+      </c>
+      <c r="M35" s="4">
+        <f t="shared" si="282"/>
+        <v>0.98110979929161757</v>
+      </c>
       <c r="T35" s="4">
         <f t="shared" ref="T35" si="283">+T17/S17-1</f>
         <v>5.2365452074708552E-2</v>
@@ -4507,11 +4695,11 @@
         <v>-0.67848654815096499</v>
       </c>
       <c r="AI35" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AJ35" s="15">
         <f>NPV(AJ34,Y29:IA29)</f>
-        <v>40189.572907846472</v>
+        <v>70067.695967178122</v>
       </c>
     </row>
     <row r="36" spans="2:36" s="4" customFormat="1">
@@ -4519,7 +4707,7 @@
         <v>23</v>
       </c>
       <c r="G36" s="4">
-        <f t="shared" ref="G36:K36" si="285">+G18/C18-1</f>
+        <f t="shared" ref="G36:M36" si="285">+G18/C18-1</f>
         <v>-0.70443349753694573</v>
       </c>
       <c r="H36" s="4">
@@ -4538,6 +4726,14 @@
         <f t="shared" si="285"/>
         <v>0.50238095238095237</v>
       </c>
+      <c r="L36" s="4">
+        <f t="shared" si="285"/>
+        <v>0.30371203599550056</v>
+      </c>
+      <c r="M36" s="4">
+        <f t="shared" si="285"/>
+        <v>0.2082901554404144</v>
+      </c>
       <c r="T36" s="4">
         <f t="shared" ref="T36" si="286">+T18/S18-1</f>
         <v>-0.32054503000029555</v>
@@ -4559,11 +4755,11 @@
         <v>-0.49212724935732644</v>
       </c>
       <c r="AI36" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AJ36" s="3">
         <f>+Main!I5</f>
-        <v>862.2</v>
+        <v>848.1</v>
       </c>
     </row>
     <row r="37" spans="2:36" s="4" customFormat="1">
@@ -4571,7 +4767,7 @@
         <v>24</v>
       </c>
       <c r="G37" s="4">
-        <f t="shared" ref="G37:K37" si="288">+G19/C19-1</f>
+        <f t="shared" ref="G37:M37" si="288">+G19/C19-1</f>
         <v>-0.13101903695408734</v>
       </c>
       <c r="H37" s="4">
@@ -4590,6 +4786,14 @@
         <f t="shared" si="288"/>
         <v>-2.448453608247414E-2</v>
       </c>
+      <c r="L37" s="4">
+        <f t="shared" si="288"/>
+        <v>-2.624671916010568E-3</v>
+      </c>
+      <c r="M37" s="4">
+        <f t="shared" si="288"/>
+        <v>-0.57780458383594691</v>
+      </c>
       <c r="T37" s="4">
         <f t="shared" ref="T37" si="289">+T19/S19-1</f>
         <v>0.31081981781826262</v>
@@ -4611,11 +4815,11 @@
         <v>-0.16971413855266559</v>
       </c>
       <c r="AI37" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AJ37" s="3">
         <f>+AJ35/AJ36</f>
-        <v>46.612819424549372</v>
+        <v>82.617257360191161</v>
       </c>
     </row>
     <row r="38" spans="2:36" s="4" customFormat="1">
@@ -4644,15 +4848,15 @@
       </c>
       <c r="L38" s="4">
         <f t="shared" si="291"/>
-        <v>0.48896221227119163</v>
+        <v>0.57600754183360814</v>
       </c>
       <c r="M38" s="4">
         <f t="shared" si="291"/>
-        <v>0.2501154277422335</v>
+        <v>0.36831343578919595</v>
       </c>
       <c r="N38" s="4">
         <f t="shared" si="291"/>
-        <v>4.2863431275448782E-2</v>
+        <v>0.21052052382524544</v>
       </c>
       <c r="T38" s="4">
         <f t="shared" ref="T38" si="292">+T20/S20-1</f>
@@ -4676,51 +4880,51 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="279"/>
-        <v>0.31451459088308242</v>
+        <v>0.41763043365179553</v>
       </c>
       <c r="Z38" s="4">
         <f t="shared" ref="Z38" si="294">+Z20/Y20-1</f>
-        <v>0.19999999999999996</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" ref="AA38" si="295">+AA20/Z20-1</f>
-        <v>0.19999999999999996</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB38" s="4">
         <f t="shared" ref="AB38" si="296">+AB20/AA20-1</f>
-        <v>0.19999999999999996</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC38" s="4">
         <f t="shared" ref="AC38" si="297">+AC20/AB20-1</f>
-        <v>0.19999999999999996</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD38" s="4">
         <f t="shared" ref="AD38" si="298">+AD20/AC20-1</f>
-        <v>0.19999999999999996</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE38" s="4">
         <f t="shared" ref="AE38" si="299">+AE20/AD20-1</f>
-        <v>0.19999999999999996</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" ref="AF38" si="300">+AF20/AE20-1</f>
-        <v>0.19999999999999996</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG38" s="4">
         <f t="shared" ref="AG38" si="301">+AG20/AF20-1</f>
-        <v>0.19999999999999996</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI38" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ38" s="16">
         <f>+Main!I4</f>
-        <v>122.82</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="2:36" s="4" customFormat="1">
       <c r="B39" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C39" s="4">
         <f>+C23/C$20</f>
@@ -4760,195 +4964,1020 @@
       </c>
       <c r="L39" s="4">
         <f t="shared" si="304"/>
-        <v>0.26787315992191207</v>
+        <v>0.25871093165844178</v>
       </c>
       <c r="M39" s="4">
         <f t="shared" ref="M39:N39" si="305">+M23/M$20</f>
-        <v>0.26787315992191207</v>
+        <v>0.24704748132080021</v>
       </c>
       <c r="N39" s="4">
         <f t="shared" si="305"/>
-        <v>0.26787315992191207</v>
+        <v>0.24704748132080021</v>
       </c>
       <c r="AI39" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ39" s="17">
         <f>+AJ37/AJ38-1</f>
-        <v>-0.62047859123473881</v>
+        <v>7.5275287828189263E-3</v>
       </c>
     </row>
     <row r="41" spans="2:36">
-      <c r="AI41" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ41" s="1">
-        <f>+Main!I9</f>
-        <v>109242.10400000001</v>
-      </c>
-    </row>
-    <row r="42" spans="2:36">
-      <c r="AJ42" s="1">
-        <f>+AJ41/Y20</f>
-        <v>14.409605867145045</v>
-      </c>
-    </row>
-    <row r="43" spans="2:36">
-      <c r="B43" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="1">
-        <v>208.4</v>
-      </c>
-      <c r="D43" s="1">
-        <v>112.5</v>
-      </c>
-      <c r="E43" s="5">
-        <v>503</v>
-      </c>
-      <c r="F43" s="1">
-        <v>546.6</v>
-      </c>
-      <c r="G43" s="1">
-        <v>324.5</v>
-      </c>
-      <c r="H43" s="1">
-        <v>306.39999999999998</v>
-      </c>
-      <c r="I43" s="1">
-        <v>536.29999999999995</v>
-      </c>
-      <c r="J43" s="1">
-        <f>1681.2-SUM(G43:I43)</f>
-        <v>514.00000000000023</v>
+      <c r="B41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="4">
+        <f t="shared" ref="C41:M41" si="306">+C22/C20</f>
+        <v>0.42157827040932133</v>
+      </c>
+      <c r="D41" s="4">
+        <f t="shared" si="306"/>
+        <v>0.38861958386158557</v>
+      </c>
+      <c r="E41" s="4">
+        <f t="shared" si="306"/>
+        <v>0.38855209361342163</v>
+      </c>
+      <c r="F41" s="4">
+        <f t="shared" si="306"/>
+        <v>0.46554504030844734</v>
+      </c>
+      <c r="G41" s="4">
+        <f t="shared" si="306"/>
+        <v>0.45464725643896969</v>
+      </c>
+      <c r="H41" s="4">
+        <f t="shared" si="306"/>
+        <v>0.46162306544111881</v>
+      </c>
+      <c r="I41" s="4">
+        <f t="shared" si="306"/>
+        <v>0.23045973220763794</v>
+      </c>
+      <c r="J41" s="4">
+        <f t="shared" si="306"/>
+        <v>0.50478705843512706</v>
+      </c>
+      <c r="K41" s="4">
+        <f t="shared" si="306"/>
+        <v>0.50250619954624598</v>
+      </c>
+      <c r="L41" s="4">
+        <f t="shared" si="306"/>
+        <v>0.50376352126015655</v>
+      </c>
+      <c r="M41" s="4">
+        <f>+M22/M20</f>
+        <v>0.51569052783803326</v>
+      </c>
+      <c r="N41" s="4">
+        <f>+N22/N20</f>
+        <v>0.51569052783803326</v>
+      </c>
+      <c r="T41" s="4">
+        <f>+T22/T20</f>
+        <v>0</v>
+      </c>
+      <c r="U41" s="4">
+        <f>+U22/U20</f>
+        <v>0.46257619218357843</v>
+      </c>
+      <c r="V41" s="4">
+        <f>+V22/V20</f>
+        <v>0.50467937022771814</v>
+      </c>
+      <c r="W41" s="4">
+        <f>+W22/W20</f>
+        <v>0.41643517257657459</v>
+      </c>
+      <c r="X41" s="4">
+        <f>+X22/X20</f>
+        <v>0.41305290170443704</v>
+      </c>
+      <c r="Y41" s="4">
+        <f>+Y22/Y20</f>
+        <v>0.50970769716406428</v>
+      </c>
+      <c r="Z41" s="4">
+        <f>+Z22/Z20</f>
+        <v>0.50970769716406417</v>
       </c>
     </row>
     <row r="44" spans="2:36">
       <c r="B44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J44" s="1">
+        <v>948.3</v>
+      </c>
+      <c r="K44" s="1">
+        <v>885.9</v>
+      </c>
+      <c r="L44" s="1">
+        <v>1224.4000000000001</v>
+      </c>
+      <c r="M44" s="1">
+        <v>2714.5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:36">
+      <c r="B45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1028.4000000000001</v>
+      </c>
+      <c r="K45" s="1">
+        <v>1144</v>
+      </c>
+      <c r="L45" s="1">
+        <v>1451.7</v>
+      </c>
+      <c r="M45" s="1">
+        <v>1546.3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:36">
+      <c r="B46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1029.7</v>
+      </c>
+      <c r="K46" s="1">
+        <v>1071.4000000000001</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1051.5999999999999</v>
+      </c>
+      <c r="M46" s="1">
+        <v>1014.5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:36">
+      <c r="B47" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J47" s="1">
+        <v>113.9</v>
+      </c>
+      <c r="K47" s="1">
+        <v>148.1</v>
+      </c>
+      <c r="L47" s="1">
+        <v>189.7</v>
+      </c>
+      <c r="M47" s="1">
+        <v>237.2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:36">
+      <c r="B48" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K48" s="1">
+        <v>588.20000000000005</v>
+      </c>
+      <c r="L48" s="1">
+        <v>595.5</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13">
+      <c r="B49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J49" s="1">
+        <v>790.5</v>
+      </c>
+      <c r="K49" s="1">
+        <v>774.7</v>
+      </c>
+      <c r="L49" s="1">
+        <v>794.5</v>
+      </c>
+      <c r="M49" s="1">
+        <v>854.8</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13">
+      <c r="B50" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J50" s="1">
+        <v>11586.9</v>
+      </c>
+      <c r="K50" s="1">
+        <v>11062.2</v>
+      </c>
+      <c r="L50" s="1">
+        <v>11062.2</v>
+      </c>
+      <c r="M50" s="1">
+        <v>11062.2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13">
+      <c r="B51" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J51" s="1">
+        <v>2710.6</v>
+      </c>
+      <c r="K51" s="1">
+        <v>2450.9</v>
+      </c>
+      <c r="L51" s="1">
+        <v>2207.1999999999998</v>
+      </c>
+      <c r="M51" s="1">
+        <v>1978.3</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13">
+      <c r="B52" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J52" s="1">
+        <v>401.2</v>
+      </c>
+      <c r="K52" s="1">
+        <v>405.9</v>
+      </c>
+      <c r="L52" s="1">
+        <v>409.9</v>
+      </c>
+      <c r="M52" s="1">
+        <v>403.5</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13">
+      <c r="B53" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1595</v>
+      </c>
+      <c r="K53" s="1">
+        <v>1492.4</v>
+      </c>
+      <c r="L53" s="1">
+        <v>1599.6</v>
+      </c>
+      <c r="M53" s="1">
+        <v>1767.7</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13">
+      <c r="B54" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J54" s="1">
+        <f>+SUM(J44:J53)</f>
+        <v>20204.5</v>
+      </c>
+      <c r="K54" s="1">
+        <f>+SUM(K44:K53)</f>
+        <v>20023.700000000004</v>
+      </c>
+      <c r="L54" s="1">
+        <f>+SUM(L44:L53)</f>
+        <v>20586.3</v>
+      </c>
+      <c r="M54" s="1">
+        <f>+SUM(M44:M53)</f>
+        <v>21579</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13">
+      <c r="B56" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J56" s="1">
+        <v>622.20000000000005</v>
+      </c>
+      <c r="K56" s="1">
+        <v>562.70000000000005</v>
+      </c>
+      <c r="L56" s="1">
+        <v>610.70000000000005</v>
+      </c>
+      <c r="M56" s="1">
+        <v>633.70000000000005</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13">
+      <c r="B57" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J57" s="1">
+        <v>972.6</v>
+      </c>
+      <c r="K57" s="1">
+        <v>939.8</v>
+      </c>
+      <c r="L57" s="1">
+        <v>1078.5</v>
+      </c>
+      <c r="M57" s="1">
+        <v>1351.1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13">
+      <c r="B58" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J58" s="1">
+        <v>302.5</v>
+      </c>
+      <c r="K58" s="1">
+        <v>183.7</v>
+      </c>
+      <c r="L58" s="1">
+        <v>210.8</v>
+      </c>
+      <c r="M58" s="1">
+        <v>252.4</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13">
+      <c r="B59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J59" s="1">
+        <v>129.5</v>
+      </c>
+      <c r="K59" s="1">
+        <v>1255.2</v>
+      </c>
+      <c r="L59" s="1">
+        <v>499.3</v>
+      </c>
+      <c r="M59" s="1">
+        <v>499.5</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13">
+      <c r="B60" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J60" s="1">
+        <v>3934.3</v>
+      </c>
+      <c r="K60" s="1">
+        <v>2977.4</v>
+      </c>
+      <c r="L60" s="1">
+        <v>3967.9</v>
+      </c>
+      <c r="M60" s="1">
+        <v>3969.4</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13">
+      <c r="B61" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J61" s="1">
+        <v>816.4</v>
+      </c>
+      <c r="K61" s="1">
+        <v>792.2</v>
+      </c>
+      <c r="L61" s="1">
+        <v>797.4</v>
+      </c>
+      <c r="M61" s="1">
+        <v>816.3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13">
+      <c r="B62" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J62" s="1">
+        <f>+SUM(J56:J61)</f>
+        <v>6777.5</v>
+      </c>
+      <c r="K62" s="1">
+        <f>+SUM(K56:K61)</f>
+        <v>6711</v>
+      </c>
+      <c r="L62" s="1">
+        <f>+SUM(L56:L61)</f>
+        <v>7164.6</v>
+      </c>
+      <c r="M62" s="1">
+        <f>+SUM(M56:M61)</f>
+        <v>7522.4000000000005</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13">
+      <c r="B63" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J63" s="1">
+        <v>13427</v>
+      </c>
+      <c r="K63" s="1">
+        <v>13312.7</v>
+      </c>
+      <c r="L63" s="1">
+        <v>13421.7</v>
+      </c>
+      <c r="M63" s="1">
+        <v>14056.6</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" s="5" customFormat="1">
+      <c r="B64" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J64" s="5">
+        <f>+J62+J63</f>
+        <v>20204.5</v>
+      </c>
+      <c r="K64" s="5">
+        <f>+K62+K63</f>
+        <v>20023.7</v>
+      </c>
+      <c r="L64" s="5">
+        <f>+L62+L63</f>
+        <v>20586.300000000003</v>
+      </c>
+      <c r="M64" s="5">
+        <f>+M62+M63</f>
+        <v>21579</v>
+      </c>
+    </row>
+    <row r="65" spans="2:36" s="5" customFormat="1"/>
+    <row r="66" spans="2:36" s="5" customFormat="1">
+      <c r="B66" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C66" s="6">
+        <f>+C59+C60</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="6">
+        <f t="shared" ref="D66:M66" si="307">+D59+D60</f>
+        <v>0</v>
+      </c>
+      <c r="E66" s="6">
+        <f t="shared" si="307"/>
+        <v>0</v>
+      </c>
+      <c r="F66" s="6">
+        <f t="shared" si="307"/>
+        <v>0</v>
+      </c>
+      <c r="G66" s="6">
+        <f t="shared" si="307"/>
+        <v>0</v>
+      </c>
+      <c r="H66" s="6">
+        <f t="shared" si="307"/>
+        <v>0</v>
+      </c>
+      <c r="I66" s="6">
+        <f t="shared" si="307"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="6">
+        <f t="shared" si="307"/>
+        <v>4063.8</v>
+      </c>
+      <c r="K66" s="6">
+        <f t="shared" si="307"/>
+        <v>4232.6000000000004</v>
+      </c>
+      <c r="L66" s="6">
+        <f t="shared" si="307"/>
+        <v>4467.2</v>
+      </c>
+      <c r="M66" s="6">
+        <f t="shared" si="307"/>
+        <v>4468.8999999999996</v>
+      </c>
+    </row>
+    <row r="67" spans="2:36" s="5" customFormat="1">
+      <c r="B67" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C67" s="6">
+        <f>+C44</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="6">
+        <f t="shared" ref="D67:M67" si="308">+D44</f>
+        <v>0</v>
+      </c>
+      <c r="E67" s="6">
+        <f t="shared" si="308"/>
+        <v>0</v>
+      </c>
+      <c r="F67" s="6">
+        <f t="shared" si="308"/>
+        <v>0</v>
+      </c>
+      <c r="G67" s="6">
+        <f t="shared" si="308"/>
+        <v>0</v>
+      </c>
+      <c r="H67" s="6">
+        <f t="shared" si="308"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="6">
+        <f t="shared" si="308"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="6">
+        <f t="shared" si="308"/>
+        <v>948.3</v>
+      </c>
+      <c r="K67" s="6">
+        <f t="shared" si="308"/>
+        <v>885.9</v>
+      </c>
+      <c r="L67" s="6">
+        <f t="shared" si="308"/>
+        <v>1224.4000000000001</v>
+      </c>
+      <c r="M67" s="6">
+        <f t="shared" si="308"/>
+        <v>2714.5</v>
+      </c>
+    </row>
+    <row r="68" spans="2:36" s="5" customFormat="1">
+      <c r="B68" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J68" s="17">
+        <f>+J46/SUM(G20:J20)</f>
+        <v>0.17854108508314118</v>
+      </c>
+      <c r="K68" s="17">
+        <f>+K46/SUM(H20:K20)</f>
+        <v>0.16478767091683716</v>
+      </c>
+      <c r="L68" s="17">
+        <f>+L46/SUM(I20:L20)</f>
+        <v>0.14535100692476743</v>
+      </c>
+      <c r="M68" s="17">
+        <f>+M46/SUM(J20:M20)</f>
+        <v>0.13017592034183209</v>
+      </c>
+    </row>
+    <row r="69" spans="2:36" s="5" customFormat="1">
+      <c r="B69" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6">
+        <f>+(J46/SUM(G21:J21)) * 365</f>
+        <v>111.02788691619155</v>
+      </c>
+      <c r="K69" s="6">
+        <f>+(K46/SUM(H21:K21)) * 365</f>
+        <v>105.83804703780889</v>
+      </c>
+      <c r="L69" s="6">
+        <f>+(L46/SUM(I21:L21)) * 365</f>
+        <v>95.836308706399336</v>
+      </c>
+      <c r="M69" s="6">
+        <f>+(M46/SUM(J21:M21)) * 365</f>
+        <v>96.35255392781869</v>
+      </c>
+    </row>
+    <row r="70" spans="2:36" s="5" customFormat="1">
+      <c r="B70" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6">
+        <f t="shared" ref="J70:L70" si="309">+(J45/SUM(G20:J20)) * 365</f>
+        <v>65.085221854247237</v>
+      </c>
+      <c r="K70" s="6">
+        <f t="shared" si="309"/>
+        <v>64.223203162249874</v>
+      </c>
+      <c r="L70" s="6">
+        <f t="shared" si="309"/>
+        <v>73.238123540062759</v>
+      </c>
+      <c r="M70" s="6">
+        <f>+(M45/SUM(J20:M20)) * 365</f>
+        <v>72.421118139940731</v>
+      </c>
+    </row>
+    <row r="71" spans="2:36" s="5" customFormat="1">
+      <c r="B71" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6">
+        <f t="shared" ref="J71:L71" si="310">+(J56/SUM(G21:J21)) * 365</f>
+        <v>67.089007710259679</v>
+      </c>
+      <c r="K71" s="6">
+        <f t="shared" si="310"/>
+        <v>55.586213429321511</v>
+      </c>
+      <c r="L71" s="6">
+        <f t="shared" si="310"/>
+        <v>55.65541434670795</v>
+      </c>
+      <c r="M71" s="6">
+        <f>+(M56/SUM(J21:M21)) * 365</f>
+        <v>60.18591761858918</v>
+      </c>
+    </row>
+    <row r="72" spans="2:36" s="5" customFormat="1">
+      <c r="B72" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6">
+        <f t="shared" ref="J72:L72" si="311">+J69+J70-J71</f>
+        <v>109.02410106017909</v>
+      </c>
+      <c r="K72" s="6">
+        <f t="shared" si="311"/>
+        <v>114.47503677073726</v>
+      </c>
+      <c r="L72" s="6">
+        <f t="shared" si="311"/>
+        <v>113.41901789975415</v>
+      </c>
+      <c r="M72" s="6">
+        <f>+M69+M70-M71</f>
+        <v>108.58775444917026</v>
+      </c>
+    </row>
+    <row r="73" spans="2:36" s="5" customFormat="1">
+      <c r="B73" s="6"/>
+    </row>
+    <row r="74" spans="2:36" s="5" customFormat="1">
+      <c r="B74" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C74" s="6">
+        <f>+C63</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="6">
+        <f t="shared" ref="D74:M74" si="312">+D63</f>
+        <v>0</v>
+      </c>
+      <c r="E74" s="6">
+        <f t="shared" si="312"/>
+        <v>0</v>
+      </c>
+      <c r="F74" s="6">
+        <f t="shared" si="312"/>
+        <v>0</v>
+      </c>
+      <c r="G74" s="6">
+        <f t="shared" si="312"/>
+        <v>0</v>
+      </c>
+      <c r="H74" s="6">
+        <f t="shared" si="312"/>
+        <v>0</v>
+      </c>
+      <c r="I74" s="6">
+        <f t="shared" si="312"/>
+        <v>0</v>
+      </c>
+      <c r="J74" s="6">
+        <f t="shared" si="312"/>
+        <v>13427</v>
+      </c>
+      <c r="K74" s="6">
+        <f t="shared" si="312"/>
+        <v>13312.7</v>
+      </c>
+      <c r="L74" s="6">
+        <f t="shared" si="312"/>
+        <v>13421.7</v>
+      </c>
+      <c r="M74" s="6">
+        <f t="shared" si="312"/>
+        <v>14056.6</v>
+      </c>
+    </row>
+    <row r="75" spans="2:36" s="5" customFormat="1">
+      <c r="B75" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" s="21"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="22">
+        <f>+SUM(J44:J47) / SUM(J56:J59)</f>
+        <v>1.5395204262877442</v>
+      </c>
+      <c r="K75" s="22">
+        <f>+SUM(K44:K47) / SUM(K56:K59)</f>
+        <v>1.1047120418848166</v>
+      </c>
+      <c r="L75" s="22">
+        <f>+SUM(L44:L47) / SUM(L56:L59)</f>
+        <v>1.6327262118117782</v>
+      </c>
+      <c r="M75" s="22">
+        <f>+SUM(M44:M47) / SUM(M56:M59)</f>
+        <v>2.0142872803010925</v>
+      </c>
+    </row>
+    <row r="76" spans="2:36" s="5" customFormat="1">
+      <c r="B76" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C76" s="18"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="24"/>
+      <c r="J76" s="25">
+        <f>+SUM(J44:J45,J47:J48)/SUM(J56:J59)</f>
+        <v>1.0314781922241956</v>
+      </c>
+      <c r="K76" s="25">
+        <f>+SUM(K44:K45,K47:K48)/SUM(K56:K59)</f>
+        <v>0.94043652682396128</v>
+      </c>
+      <c r="L76" s="25">
+        <f>+SUM(L44:L45,L47:L48)/SUM(L56:L59)</f>
+        <v>1.4426291001542115</v>
+      </c>
+      <c r="M76" s="25">
+        <f>+SUM(M44:M45,M47:M48)/SUM(M56:M59)</f>
+        <v>1.6435853400080389</v>
+      </c>
+    </row>
+    <row r="77" spans="2:36" s="5" customFormat="1"/>
+    <row r="78" spans="2:36" s="5" customFormat="1"/>
+    <row r="79" spans="2:36">
+      <c r="AI79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ79" s="1">
+        <f>+Main!I9</f>
+        <v>71298.599999999991</v>
+      </c>
+    </row>
+    <row r="80" spans="2:36">
+      <c r="AJ80" s="1">
+        <f>+AJ79/Y20</f>
+        <v>8.7205812204161006</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13">
+      <c r="B81" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C81" s="1">
+        <v>208.4</v>
+      </c>
+      <c r="D81" s="1">
+        <v>112.5</v>
+      </c>
+      <c r="E81" s="5">
+        <v>503</v>
+      </c>
+      <c r="F81" s="1">
+        <v>546.6</v>
+      </c>
+      <c r="G81" s="1">
+        <v>324.5</v>
+      </c>
+      <c r="H81" s="1">
+        <v>306.39999999999998</v>
+      </c>
+      <c r="I81" s="1">
+        <v>536.29999999999995</v>
+      </c>
+      <c r="J81" s="1">
+        <f>1681.2-SUM(G81:I81)</f>
+        <v>514.00000000000023</v>
+      </c>
+      <c r="K81" s="1">
+        <v>332.9</v>
+      </c>
+      <c r="L81" s="1">
+        <v>461.6</v>
+      </c>
+      <c r="M81" s="1">
+        <v>582.29999999999995</v>
+      </c>
+    </row>
+    <row r="82" spans="2:13">
+      <c r="B82" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C82" s="1">
         <f>+-99.8-2.8</f>
         <v>-102.6</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D82" s="1">
         <f>+-111.1-0.2</f>
         <v>-111.3</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E82" s="1">
         <f>+-54.4-0.3</f>
         <v>-54.699999999999996</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F82" s="1">
         <f>+-71-10.6</f>
         <v>-81.599999999999994</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G82" s="1">
         <f>+-91.5-0.5</f>
         <v>-92</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H82" s="1">
         <f>+-48.2-5.2</f>
         <v>-53.400000000000006</v>
       </c>
-      <c r="I44" s="1">
+      <c r="I82" s="1">
         <f>+-75-0.5</f>
         <v>-75.5</v>
       </c>
-      <c r="J44" s="1">
-        <f>+-284.6-SUM(G44:I44)</f>
+      <c r="J82" s="1">
+        <f>+-284.6-SUM(G82:I82)</f>
         <v>-63.700000000000017</v>
       </c>
-    </row>
-    <row r="45" spans="2:36" s="5" customFormat="1">
-      <c r="B45" s="5" t="s">
+      <c r="K82" s="1">
+        <v>-118.8</v>
+      </c>
+      <c r="L82" s="1">
+        <v>-47.5</v>
+      </c>
+      <c r="M82" s="1">
+        <v>-73.5</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13" s="5" customFormat="1">
+      <c r="B83" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="5">
-        <f t="shared" ref="C45:H45" si="306">SUM(C43:C44)</f>
+      <c r="C83" s="5">
+        <f t="shared" ref="C83:H83" si="313">SUM(C81:C82)</f>
         <v>105.80000000000001</v>
       </c>
-      <c r="D45" s="5">
-        <f t="shared" si="306"/>
+      <c r="D83" s="5">
+        <f t="shared" si="313"/>
         <v>1.2000000000000028</v>
       </c>
-      <c r="E45" s="5">
-        <f t="shared" si="306"/>
+      <c r="E83" s="5">
+        <f t="shared" si="313"/>
         <v>448.3</v>
       </c>
-      <c r="F45" s="5">
-        <f t="shared" si="306"/>
+      <c r="F83" s="5">
+        <f t="shared" si="313"/>
         <v>465</v>
       </c>
-      <c r="G45" s="5">
-        <f t="shared" si="306"/>
+      <c r="G83" s="5">
+        <f t="shared" si="313"/>
         <v>232.5</v>
       </c>
-      <c r="H45" s="5">
-        <f t="shared" si="306"/>
+      <c r="H83" s="5">
+        <f t="shared" si="313"/>
         <v>252.99999999999997</v>
       </c>
-      <c r="I45" s="5">
-        <f>SUM(I43:I44)</f>
+      <c r="I83" s="5">
+        <f>SUM(I81:I82)</f>
         <v>460.79999999999995</v>
       </c>
-      <c r="J45" s="5">
-        <f>SUM(J43:J44)</f>
+      <c r="J83" s="5">
+        <f>SUM(J81:J82)</f>
         <v>450.30000000000018</v>
       </c>
-    </row>
-    <row r="47" spans="2:36">
-      <c r="B47" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F47" s="1">
-        <f t="shared" ref="F47:H47" si="307">SUM(C45:F45)</f>
+      <c r="K83" s="5">
+        <f>SUM(K81:K82)</f>
+        <v>214.09999999999997</v>
+      </c>
+      <c r="L83" s="5">
+        <f>SUM(L81:L82)</f>
+        <v>414.1</v>
+      </c>
+      <c r="M83" s="5">
+        <f>SUM(M81:M82)</f>
+        <v>508.79999999999995</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13">
+      <c r="B85" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F85" s="1">
+        <f t="shared" ref="F85:H85" si="314">SUM(C83:F83)</f>
         <v>1020.3000000000001</v>
       </c>
-      <c r="G47" s="1">
-        <f t="shared" si="307"/>
+      <c r="G85" s="1">
+        <f t="shared" si="314"/>
         <v>1147</v>
       </c>
-      <c r="H47" s="1">
-        <f t="shared" si="307"/>
+      <c r="H85" s="1">
+        <f t="shared" si="314"/>
         <v>1398.8</v>
       </c>
-      <c r="I47" s="1">
-        <f>SUM(F45:I45)</f>
+      <c r="I85" s="1">
+        <f>SUM(F83:I83)</f>
         <v>1411.3</v>
       </c>
-      <c r="J47" s="1">
-        <f>SUM(G45:J45)</f>
+      <c r="J85" s="1">
+        <f>SUM(G83:J83)</f>
         <v>1396.6000000000001</v>
       </c>
-    </row>
-    <row r="48" spans="2:36">
-      <c r="F48" s="1">
-        <f t="shared" ref="F48:H48" si="308">+SUM(C29:F29)</f>
+      <c r="K85" s="1">
+        <f>SUM(H83:L83)</f>
+        <v>1792.3000000000002</v>
+      </c>
+      <c r="L85" s="1">
+        <f>SUM(I83:L83)</f>
+        <v>1539.3000000000002</v>
+      </c>
+      <c r="M85" s="1">
+        <f t="shared" ref="K85:M85" si="315">SUM(J83:M83)</f>
+        <v>1587.3</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13">
+      <c r="B86" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F86" s="1">
+        <f>+SUM(C29:F29)</f>
         <v>-802.3</v>
       </c>
-      <c r="G48" s="1">
-        <f t="shared" si="308"/>
+      <c r="G86" s="1">
+        <f>+SUM(D29:G29)</f>
         <v>-904.80000000000018</v>
       </c>
-      <c r="H48" s="1">
-        <f t="shared" si="308"/>
+      <c r="H86" s="1">
+        <f>+SUM(E29:H29)</f>
         <v>-928.60000000000025</v>
       </c>
-      <c r="I48" s="1">
+      <c r="I86" s="1">
         <f>+SUM(F29:I29)</f>
         <v>-1085.7000000000003</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J86" s="1">
         <f>+SUM(G29:J29)</f>
         <v>-531.10000000000093</v>
+      </c>
+      <c r="K86" s="1">
+        <f>+SUM(H29:K29)</f>
+        <v>-154.00000000000074</v>
+      </c>
+      <c r="L86" s="1">
+        <f>+SUM(I29:L29)</f>
+        <v>238.79999999999905</v>
+      </c>
+      <c r="M86" s="1">
+        <f>+SUM(J29:M29)</f>
+        <v>2467.6999999999994</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="U20 S20:T20" formulaRange="1"/>
-    <ignoredError sqref="F22:F29" formula="1"/>
+    <ignoredError sqref="U20 S20:T20 J19:K19 J20:K20 O20 J21:K21 N21 J15:K15 N15:O15 J16:K16 N16:O16 J17:K17 N17:O17 J18:K18 N18:O18 N19:O19 H75:M75 J81:L89" formulaRange="1"/>
+    <ignoredError sqref="F22:F29 V22:AH31 P32:Y38 P29:U31 K29:O38 K22:N22 J39:V40 N44:V44 N61:V61 N62:V62 Q23:U28 K23:N28 Q22:U22 J42:V43 J41:S41" formula="1"/>
+    <ignoredError sqref="J28 J29:J38 J26 J27 J24 J23 J25 J22" formula="1" formulaRange="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
